--- a/fixtures/product-prototype/workbooks/criminal-courts-2024-25-cube-2-normalized.xlsx
+++ b/fixtures/product-prototype/workbooks/criminal-courts-2024-25-cube-2-normalized.xlsx
@@ -18702,19 +18702,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63DDECB6-FFCE-4324-AFDF-E3CF7EF9B96E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{63DDECB6-FFCE-4324-AFDF-E3CF7EF9B96E}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:J238"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15.75" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15.75" zeroHeight="1" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.125" customWidth="1"/>
     <col min="2" max="10" width="10.625" customWidth="1"/>
-    <col min="11" max="16384" width="8.625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="65.25" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="72" t="s">
         <v>253</v>
       </c>
@@ -18728,7 +18727,7 @@
       <c r="I1" s="72"/>
       <c r="J1" s="72"/>
     </row>
-    <row r="2" spans="1:10" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="36" customHeight="1" thickBot="1" ns3:dyDescent="0.35">
       <c r="A2" s="71" t="s">
         <v>105</v>
       </c>
@@ -18742,7 +18741,7 @@
       <c r="I2" s="71"/>
       <c r="J2" s="71"/>
     </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15.75" customHeight="1" thickTop="1" ns3:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>83</v>
       </c>
@@ -18756,8 +18755,8 @@
       <c r="I3" s="58"/>
       <c r="J3" s="58"/>
     </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.75" customHeight="1" ns3:dyDescent="0.25"/>
+    <row r="5" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -18789,7 +18788,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="67" t="s">
         <v>24</v>
@@ -18803,7 +18802,7 @@
       <c r="I6" s="67"/>
       <c r="J6" s="67"/>
     </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -18817,7 +18816,7 @@
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
     </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>6</v>
       </c>
@@ -18849,7 +18848,7 @@
         <v>339462</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>7</v>
       </c>
@@ -18881,7 +18880,7 @@
         <v>105702</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>26</v>
       </c>
@@ -18913,7 +18912,7 @@
         <v>4326</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B11" s="24"/>
       <c r="C11" s="24"/>
       <c r="D11" s="24"/>
@@ -18924,7 +18923,7 @@
       <c r="I11" s="24"/>
       <c r="J11" s="24"/>
     </row>
-    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -18938,7 +18937,7 @@
       <c r="I12" s="24"/>
       <c r="J12" s="24"/>
     </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>27</v>
       </c>
@@ -18970,7 +18969,7 @@
         <v>37811</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>8</v>
       </c>
@@ -19002,7 +19001,7 @@
         <v>57981</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>9</v>
       </c>
@@ -19034,7 +19033,7 @@
         <v>59927</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>10</v>
       </c>
@@ -19066,7 +19065,7 @@
         <v>63287</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>11</v>
       </c>
@@ -19098,7 +19097,7 @@
         <v>59223</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>12</v>
       </c>
@@ -19130,7 +19129,7 @@
         <v>52660</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>13</v>
       </c>
@@ -19162,7 +19161,7 @@
         <v>40150</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>14</v>
       </c>
@@ -19194,7 +19193,7 @@
         <v>30717</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>28</v>
       </c>
@@ -19226,7 +19225,7 @@
         <v>42182</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>16</v>
       </c>
@@ -19258,7 +19257,7 @@
         <v>36.700000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>17</v>
       </c>
@@ -19290,7 +19289,7 @@
         <v>35.200000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
@@ -19301,7 +19300,7 @@
       <c r="I24" s="16"/>
       <c r="J24" s="16"/>
     </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A25" t="s">
         <v>81</v>
       </c>
@@ -19315,7 +19314,7 @@
       <c r="I25" s="16"/>
       <c r="J25" s="16"/>
     </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>30</v>
       </c>
@@ -19347,7 +19346,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>31</v>
       </c>
@@ -19379,7 +19378,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -19390,7 +19389,7 @@
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
     </row>
-    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A29" t="s">
         <v>162</v>
       </c>
@@ -19404,7 +19403,7 @@
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
     </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>163</v>
       </c>
@@ -19436,7 +19435,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>89</v>
       </c>
@@ -19468,7 +19467,7 @@
         <v>52711</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>90</v>
       </c>
@@ -19500,7 +19499,7 @@
         <v>5517</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>164</v>
       </c>
@@ -19532,7 +19531,7 @@
         <v>16295</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>92</v>
       </c>
@@ -19564,7 +19563,7 @@
         <v>2684</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>93</v>
       </c>
@@ -19596,7 +19595,7 @@
         <v>10486</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>94</v>
       </c>
@@ -19628,7 +19627,7 @@
         <v>36251</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>95</v>
       </c>
@@ -19660,7 +19659,7 @@
         <v>8181</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>96</v>
       </c>
@@ -19692,7 +19691,7 @@
         <v>28760</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>97</v>
       </c>
@@ -19724,7 +19723,7 @@
         <v>13833</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>98</v>
       </c>
@@ -19756,7 +19755,7 @@
         <v>13640</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A41" s="10" t="s">
         <v>99</v>
       </c>
@@ -19788,7 +19787,7 @@
         <v>18017</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>187</v>
       </c>
@@ -19820,7 +19819,7 @@
         <v>189339</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>194</v>
       </c>
@@ -19852,7 +19851,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>100</v>
       </c>
@@ -19884,7 +19883,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>101</v>
       </c>
@@ -19916,7 +19915,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A46" s="10" t="s">
         <v>102</v>
       </c>
@@ -19948,7 +19947,7 @@
         <v>3034</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B47" s="24"/>
       <c r="C47" s="24"/>
       <c r="D47" s="24"/>
@@ -19959,7 +19958,7 @@
       <c r="I47" s="24"/>
       <c r="J47" s="24"/>
     </row>
-    <row r="48" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A48" t="s">
         <v>32</v>
       </c>
@@ -19973,7 +19972,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="25"/>
     </row>
-    <row r="49" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>33</v>
       </c>
@@ -20005,7 +20004,7 @@
         <v>47592</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>34</v>
       </c>
@@ -20037,7 +20036,7 @@
         <v>9232</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>35</v>
       </c>
@@ -20069,7 +20068,7 @@
         <v>13201</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A52" s="10" t="s">
         <v>196</v>
       </c>
@@ -20101,7 +20100,7 @@
         <v>10819</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>235</v>
       </c>
@@ -20133,7 +20132,7 @@
         <v>36928</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A54" s="10" t="s">
         <v>243</v>
       </c>
@@ -20165,7 +20164,7 @@
         <v>238335</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A55" s="12" t="s">
         <v>111</v>
       </c>
@@ -20197,7 +20196,7 @@
         <v>235149</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A56" s="10" t="s">
         <v>38</v>
       </c>
@@ -20229,7 +20228,7 @@
         <v>46972</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>254</v>
       </c>
@@ -20261,7 +20260,7 @@
         <v>47863</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A58" s="11" t="s">
         <v>255</v>
       </c>
@@ -20293,7 +20292,7 @@
         <v>451045</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A59" s="9"/>
       <c r="B59" s="67" t="s">
         <v>40</v>
@@ -20307,7 +20306,7 @@
       <c r="I59" s="67"/>
       <c r="J59" s="67"/>
     </row>
-    <row r="60" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A60" t="s">
         <v>25</v>
       </c>
@@ -20321,7 +20320,7 @@
       <c r="I60" s="23"/>
       <c r="J60" s="23"/>
     </row>
-    <row r="61" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A61" s="10" t="s">
         <v>6</v>
       </c>
@@ -20353,7 +20352,7 @@
         <v>11052</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A62" s="10" t="s">
         <v>7</v>
       </c>
@@ -20385,7 +20384,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A63" s="10" t="s">
         <v>26</v>
       </c>
@@ -20417,7 +20416,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B64" s="13"/>
       <c r="C64" s="13"/>
       <c r="D64" s="13"/>
@@ -20428,7 +20427,7 @@
       <c r="I64" s="13"/>
       <c r="J64" s="13"/>
     </row>
-    <row r="65" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A65" t="s">
         <v>15</v>
       </c>
@@ -20442,7 +20441,7 @@
       <c r="I65" s="13"/>
       <c r="J65" s="13"/>
     </row>
-    <row r="66" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A66" s="10" t="s">
         <v>27</v>
       </c>
@@ -20474,7 +20473,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A67" s="10" t="s">
         <v>8</v>
       </c>
@@ -20506,7 +20505,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A68" s="10" t="s">
         <v>9</v>
       </c>
@@ -20538,7 +20537,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A69" s="10" t="s">
         <v>10</v>
       </c>
@@ -20570,7 +20569,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A70" s="10" t="s">
         <v>11</v>
       </c>
@@ -20602,7 +20601,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A71" s="10" t="s">
         <v>12</v>
       </c>
@@ -20634,7 +20633,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A72" s="10" t="s">
         <v>13</v>
       </c>
@@ -20666,7 +20665,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A73" s="10" t="s">
         <v>14</v>
       </c>
@@ -20698,7 +20697,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A74" s="10" t="s">
         <v>28</v>
       </c>
@@ -20730,7 +20729,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A75" s="10" t="s">
         <v>16</v>
       </c>
@@ -20762,7 +20761,7 @@
         <v>37.299999999999997</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A76" s="10" t="s">
         <v>17</v>
       </c>
@@ -20794,7 +20793,7 @@
         <v>35.200000000000003</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B77" s="16"/>
       <c r="C77" s="16"/>
       <c r="D77" s="16"/>
@@ -20805,7 +20804,7 @@
       <c r="I77" s="16"/>
       <c r="J77" s="16"/>
     </row>
-    <row r="78" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -20819,7 +20818,7 @@
       <c r="I78" s="16"/>
       <c r="J78" s="16"/>
     </row>
-    <row r="79" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A79" s="10" t="s">
         <v>30</v>
       </c>
@@ -20851,7 +20850,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A80" s="10" t="s">
         <v>31</v>
       </c>
@@ -20883,7 +20882,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B81" s="13"/>
       <c r="C81" s="13"/>
       <c r="D81" s="13"/>
@@ -20894,7 +20893,7 @@
       <c r="I81" s="13"/>
       <c r="J81" s="13"/>
     </row>
-    <row r="82" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>162</v>
       </c>
@@ -20908,7 +20907,7 @@
       <c r="I82" s="13"/>
       <c r="J82" s="13"/>
     </row>
-    <row r="83" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A83" s="10" t="s">
         <v>163</v>
       </c>
@@ -20940,7 +20939,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A84" s="10" t="s">
         <v>89</v>
       </c>
@@ -20972,7 +20971,7 @@
         <v>2289</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A85" s="10" t="s">
         <v>90</v>
       </c>
@@ -21004,7 +21003,7 @@
         <v>2610</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A86" s="10" t="s">
         <v>164</v>
       </c>
@@ -21036,7 +21035,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A87" s="10" t="s">
         <v>92</v>
       </c>
@@ -21068,7 +21067,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A88" s="10" t="s">
         <v>93</v>
       </c>
@@ -21100,7 +21099,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A89" s="10" t="s">
         <v>94</v>
       </c>
@@ -21132,7 +21131,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A90" s="10" t="s">
         <v>95</v>
       </c>
@@ -21164,7 +21163,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A91" s="10" t="s">
         <v>96</v>
       </c>
@@ -21196,7 +21195,7 @@
         <v>2615</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A92" s="10" t="s">
         <v>97</v>
       </c>
@@ -21228,7 +21227,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A93" s="10" t="s">
         <v>98</v>
       </c>
@@ -21260,7 +21259,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A94" s="10" t="s">
         <v>99</v>
       </c>
@@ -21292,7 +21291,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A95" s="10" t="s">
         <v>187</v>
       </c>
@@ -21324,7 +21323,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A96" s="10" t="s">
         <v>194</v>
       </c>
@@ -21356,7 +21355,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A97" s="10" t="s">
         <v>100</v>
       </c>
@@ -21388,7 +21387,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A98" s="10" t="s">
         <v>101</v>
       </c>
@@ -21420,7 +21419,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A99" s="10" t="s">
         <v>102</v>
       </c>
@@ -21452,7 +21451,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
       <c r="D100" s="14"/>
@@ -21463,7 +21462,7 @@
       <c r="I100" s="14"/>
       <c r="J100" s="14"/>
     </row>
-    <row r="101" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A101" t="s">
         <v>32</v>
       </c>
@@ -21477,7 +21476,7 @@
       <c r="I101" s="14"/>
       <c r="J101" s="14"/>
     </row>
-    <row r="102" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A102" s="10" t="s">
         <v>33</v>
       </c>
@@ -21509,7 +21508,7 @@
         <v>9385</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A103" s="10" t="s">
         <v>34</v>
       </c>
@@ -21541,7 +21540,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A104" s="10" t="s">
         <v>35</v>
       </c>
@@ -21573,7 +21572,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A105" s="10" t="s">
         <v>36</v>
       </c>
@@ -21605,7 +21604,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A106" s="10" t="s">
         <v>37</v>
       </c>
@@ -21637,7 +21636,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A107" s="10" t="s">
         <v>243</v>
       </c>
@@ -21669,7 +21668,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A108" s="12" t="s">
         <v>111</v>
       </c>
@@ -21701,7 +21700,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A109" s="10" t="s">
         <v>38</v>
       </c>
@@ -21733,7 +21732,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A110" s="10" t="s">
         <v>254</v>
       </c>
@@ -21765,7 +21764,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A111" s="11" t="s">
         <v>255</v>
       </c>
@@ -21797,7 +21796,7 @@
         <v>12748</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A112" s="9"/>
       <c r="B112" s="67" t="s">
         <v>41</v>
@@ -21811,7 +21810,7 @@
       <c r="I112" s="67"/>
       <c r="J112" s="67"/>
     </row>
-    <row r="113" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A113" t="s">
         <v>25</v>
       </c>
@@ -21825,7 +21824,7 @@
       <c r="I113" s="23"/>
       <c r="J113" s="23"/>
     </row>
-    <row r="114" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A114" s="10" t="s">
         <v>6</v>
       </c>
@@ -21857,7 +21856,7 @@
         <v>314291</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A115" s="10" t="s">
         <v>7</v>
       </c>
@@ -21889,7 +21888,7 @@
         <v>99371</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A116" s="10" t="s">
         <v>26</v>
       </c>
@@ -21921,7 +21920,7 @@
         <v>4271</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B117" s="24"/>
       <c r="C117" s="24"/>
       <c r="D117" s="24"/>
@@ -21932,7 +21931,7 @@
       <c r="I117" s="24"/>
       <c r="J117" s="24"/>
     </row>
-    <row r="118" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A118" t="s">
         <v>15</v>
       </c>
@@ -21946,7 +21945,7 @@
       <c r="I118" s="24"/>
       <c r="J118" s="24"/>
     </row>
-    <row r="119" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A119" s="10" t="s">
         <v>27</v>
       </c>
@@ -21978,7 +21977,7 @@
         <v>18601</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A120" s="10" t="s">
         <v>8</v>
       </c>
@@ -22010,7 +22009,7 @@
         <v>56132</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A121" s="10" t="s">
         <v>9</v>
       </c>
@@ -22042,7 +22041,7 @@
         <v>57932</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A122" s="10" t="s">
         <v>10</v>
       </c>
@@ -22074,7 +22073,7 @@
         <v>61106</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A123" s="10" t="s">
         <v>11</v>
       </c>
@@ -22106,7 +22105,7 @@
         <v>57298</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A124" s="10" t="s">
         <v>12</v>
       </c>
@@ -22138,7 +22137,7 @@
         <v>51196</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A125" s="10" t="s">
         <v>13</v>
       </c>
@@ -22170,7 +22169,7 @@
         <v>39083</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A126" s="10" t="s">
         <v>14</v>
       </c>
@@ -22202,7 +22201,7 @@
         <v>29960</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A127" s="10" t="s">
         <v>28</v>
       </c>
@@ -22234,7 +22233,7 @@
         <v>40971</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A128" s="10" t="s">
         <v>16</v>
       </c>
@@ -22266,7 +22265,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A129" s="10" t="s">
         <v>17</v>
       </c>
@@ -22298,7 +22297,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B130" s="16"/>
       <c r="C130" s="16"/>
       <c r="D130" s="16"/>
@@ -22309,7 +22308,7 @@
       <c r="I130" s="16"/>
       <c r="J130" s="16"/>
     </row>
-    <row r="131" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A131" t="s">
         <v>81</v>
       </c>
@@ -22323,7 +22322,7 @@
       <c r="I131" s="16"/>
       <c r="J131" s="16"/>
     </row>
-    <row r="132" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A132" s="10" t="s">
         <v>30</v>
       </c>
@@ -22355,7 +22354,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A133" s="10" t="s">
         <v>31</v>
       </c>
@@ -22387,7 +22386,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B134" s="13"/>
       <c r="C134" s="13"/>
       <c r="D134" s="13"/>
@@ -22398,7 +22397,7 @@
       <c r="I134" s="13"/>
       <c r="J134" s="13"/>
     </row>
-    <row r="135" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>162</v>
       </c>
@@ -22412,7 +22411,7 @@
       <c r="I135" s="13"/>
       <c r="J135" s="13"/>
     </row>
-    <row r="136" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A136" s="10" t="s">
         <v>163</v>
       </c>
@@ -22444,7 +22443,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A137" s="10" t="s">
         <v>89</v>
       </c>
@@ -22476,7 +22475,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A138" s="10" t="s">
         <v>90</v>
       </c>
@@ -22508,7 +22507,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A139" s="10" t="s">
         <v>164</v>
       </c>
@@ -22540,7 +22539,7 @@
         <v>14715</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A140" s="10" t="s">
         <v>92</v>
       </c>
@@ -22572,7 +22571,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A141" s="10" t="s">
         <v>93</v>
       </c>
@@ -22604,7 +22603,7 @@
         <v>6853</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A142" s="10" t="s">
         <v>94</v>
       </c>
@@ -22636,7 +22635,7 @@
         <v>31962</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A143" s="10" t="s">
         <v>95</v>
       </c>
@@ -22668,7 +22667,7 @@
         <v>7515</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A144" s="10" t="s">
         <v>96</v>
       </c>
@@ -22700,7 +22699,7 @@
         <v>25705</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A145" s="10" t="s">
         <v>97</v>
       </c>
@@ -22732,7 +22731,7 @@
         <v>12773</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A146" s="10" t="s">
         <v>98</v>
       </c>
@@ -22764,7 +22763,7 @@
         <v>12245</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A147" s="10" t="s">
         <v>99</v>
       </c>
@@ -22796,7 +22795,7 @@
         <v>17009</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A148" s="10" t="s">
         <v>187</v>
       </c>
@@ -22828,7 +22827,7 @@
         <v>187432</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A149" s="10" t="s">
         <v>194</v>
       </c>
@@ -22860,7 +22859,7 @@
         <v>45476</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A150" s="10" t="s">
         <v>100</v>
       </c>
@@ -22892,7 +22891,7 @@
         <v>3331</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A151" s="10" t="s">
         <v>101</v>
       </c>
@@ -22924,7 +22923,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A152" s="10" t="s">
         <v>102</v>
       </c>
@@ -22956,7 +22955,7 @@
         <v>3018</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B153" s="24"/>
       <c r="C153" s="24"/>
       <c r="D153" s="24"/>
@@ -22967,7 +22966,7 @@
       <c r="I153" s="24"/>
       <c r="J153" s="24"/>
     </row>
-    <row r="154" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A154" t="s">
         <v>32</v>
       </c>
@@ -22981,7 +22980,7 @@
       <c r="I154" s="25"/>
       <c r="J154" s="25"/>
     </row>
-    <row r="155" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A155" s="10" t="s">
         <v>33</v>
       </c>
@@ -23013,7 +23012,7 @@
         <v>37145</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A156" s="10" t="s">
         <v>34</v>
       </c>
@@ -23045,7 +23044,7 @@
         <v>7788</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A157" s="10" t="s">
         <v>35</v>
       </c>
@@ -23077,7 +23076,7 @@
         <v>11767</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A158" s="10" t="s">
         <v>36</v>
       </c>
@@ -23109,7 +23108,7 @@
         <v>9896</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A159" s="10" t="s">
         <v>37</v>
       </c>
@@ -23141,7 +23140,7 @@
         <v>32993</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A160" s="10" t="s">
         <v>243</v>
       </c>
@@ -23173,7 +23172,7 @@
         <v>237520</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A161" s="12" t="s">
         <v>111</v>
       </c>
@@ -23205,7 +23204,7 @@
         <v>234389</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A162" s="10" t="s">
         <v>38</v>
       </c>
@@ -23237,7 +23236,7 @@
         <v>43810</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A163" s="10" t="s">
         <v>39</v>
       </c>
@@ -23269,7 +23268,7 @@
         <v>38351</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A164" s="11" t="s">
         <v>241</v>
       </c>
@@ -23301,7 +23300,7 @@
         <v>419318</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A165" s="9"/>
       <c r="B165" s="67" t="s">
         <v>42</v>
@@ -23315,7 +23314,7 @@
       <c r="I165" s="67"/>
       <c r="J165" s="67"/>
     </row>
-    <row r="166" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A166" t="s">
         <v>25</v>
       </c>
@@ -23329,7 +23328,7 @@
       <c r="I166" s="23"/>
       <c r="J166" s="23"/>
     </row>
-    <row r="167" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A167" s="10" t="s">
         <v>6</v>
       </c>
@@ -23361,7 +23360,7 @@
         <v>14122</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A168" s="10" t="s">
         <v>7</v>
       </c>
@@ -23393,7 +23392,7 @@
         <v>4721</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B169" s="24"/>
       <c r="C169" s="24"/>
       <c r="D169" s="24"/>
@@ -23404,7 +23403,7 @@
       <c r="I169" s="24"/>
       <c r="J169" s="24"/>
     </row>
-    <row r="170" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A170" t="s">
         <v>15</v>
       </c>
@@ -23418,7 +23417,7 @@
       <c r="I170" s="24"/>
       <c r="J170" s="24"/>
     </row>
-    <row r="171" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A171" s="10" t="s">
         <v>43</v>
       </c>
@@ -23450,7 +23449,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A172" s="10" t="s">
         <v>44</v>
       </c>
@@ -23482,7 +23481,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A173" s="10" t="s">
         <v>45</v>
       </c>
@@ -23514,7 +23513,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A174" s="10" t="s">
         <v>46</v>
       </c>
@@ -23546,7 +23545,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A175" s="10" t="s">
         <v>47</v>
       </c>
@@ -23578,7 +23577,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A176" s="10" t="s">
         <v>48</v>
       </c>
@@ -23610,7 +23609,7 @@
         <v>3704</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A177" s="10" t="s">
         <v>49</v>
       </c>
@@ -23642,7 +23641,7 @@
         <v>4417</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A178" s="10" t="s">
         <v>50</v>
       </c>
@@ -23674,7 +23673,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A179" s="10" t="s">
         <v>51</v>
       </c>
@@ -23706,7 +23705,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A180" s="10" t="s">
         <v>52</v>
       </c>
@@ -23738,7 +23737,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A181" s="10" t="s">
         <v>8</v>
       </c>
@@ -23770,7 +23769,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A182" s="10" t="s">
         <v>53</v>
       </c>
@@ -23802,7 +23801,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A183" s="10" t="s">
         <v>16</v>
       </c>
@@ -23834,7 +23833,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A184" s="10" t="s">
         <v>17</v>
       </c>
@@ -23866,7 +23865,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B185" s="16"/>
       <c r="C185" s="16"/>
       <c r="D185" s="16"/>
@@ -23877,7 +23876,7 @@
       <c r="I185" s="16"/>
       <c r="J185" s="16"/>
     </row>
-    <row r="186" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A186" t="s">
         <v>81</v>
       </c>
@@ -23891,7 +23890,7 @@
       <c r="I186" s="16"/>
       <c r="J186" s="16"/>
     </row>
-    <row r="187" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A187" s="10" t="s">
         <v>30</v>
       </c>
@@ -23923,7 +23922,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A188" s="10" t="s">
         <v>31</v>
       </c>
@@ -23955,7 +23954,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B189" s="13"/>
       <c r="C189" s="13"/>
       <c r="D189" s="13"/>
@@ -23966,7 +23965,7 @@
       <c r="I189" s="13"/>
       <c r="J189" s="13"/>
     </row>
-    <row r="190" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A190" t="s">
         <v>162</v>
       </c>
@@ -23980,7 +23979,7 @@
       <c r="I190" s="13"/>
       <c r="J190" s="13"/>
     </row>
-    <row r="191" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A191" s="10" t="s">
         <v>163</v>
       </c>
@@ -24012,7 +24011,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A192" s="10" t="s">
         <v>89</v>
       </c>
@@ -24044,7 +24043,7 @@
         <v>4291</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A193" s="10" t="s">
         <v>90</v>
       </c>
@@ -24076,7 +24075,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A194" s="10" t="s">
         <v>164</v>
       </c>
@@ -24108,7 +24107,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A195" s="10" t="s">
         <v>92</v>
       </c>
@@ -24140,7 +24139,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A196" s="10" t="s">
         <v>93</v>
       </c>
@@ -24172,7 +24171,7 @@
         <v>2568</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A197" s="10" t="s">
         <v>94</v>
       </c>
@@ -24204,7 +24203,7 @@
         <v>3920</v>
       </c>
     </row>
-    <row r="198" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A198" s="10" t="s">
         <v>95</v>
       </c>
@@ -24236,7 +24235,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A199" s="10" t="s">
         <v>96</v>
       </c>
@@ -24268,7 +24267,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A200" s="10" t="s">
         <v>97</v>
       </c>
@@ -24300,7 +24299,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A201" s="10" t="s">
         <v>98</v>
       </c>
@@ -24332,7 +24331,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A202" s="10" t="s">
         <v>99</v>
       </c>
@@ -24364,7 +24363,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A203" s="10" t="s">
         <v>187</v>
       </c>
@@ -24396,7 +24395,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A204" s="10" t="s">
         <v>194</v>
       </c>
@@ -24428,7 +24427,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A205" s="10" t="s">
         <v>100</v>
       </c>
@@ -24460,7 +24459,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="206" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A206" s="10" t="s">
         <v>101</v>
       </c>
@@ -24492,7 +24491,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A207" s="10" t="s">
         <v>102</v>
       </c>
@@ -24524,7 +24523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B208" s="13"/>
       <c r="C208" s="13"/>
       <c r="D208" s="13"/>
@@ -24535,7 +24534,7 @@
       <c r="I208" s="13"/>
       <c r="J208" s="13"/>
     </row>
-    <row r="209" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A209" t="s">
         <v>32</v>
       </c>
@@ -24549,7 +24548,7 @@
       <c r="I209" s="25"/>
       <c r="J209" s="25"/>
     </row>
-    <row r="210" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A210" s="10" t="s">
         <v>33</v>
       </c>
@@ -24581,7 +24580,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A211" s="10" t="s">
         <v>34</v>
       </c>
@@ -24613,7 +24612,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A212" s="10" t="s">
         <v>35</v>
       </c>
@@ -24645,7 +24644,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A213" s="10" t="s">
         <v>196</v>
       </c>
@@ -24677,7 +24676,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A214" s="10" t="s">
         <v>235</v>
       </c>
@@ -24709,7 +24708,7 @@
         <v>3539</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A215" s="10" t="s">
         <v>243</v>
       </c>
@@ -24741,7 +24740,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A216" s="12" t="s">
         <v>111</v>
       </c>
@@ -24773,7 +24772,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A217" s="10" t="s">
         <v>38</v>
       </c>
@@ -24805,7 +24804,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A218" s="10" t="s">
         <v>39</v>
       </c>
@@ -24837,7 +24836,7 @@
         <v>9115</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A219" s="12" t="s">
         <v>239</v>
       </c>
@@ -24869,7 +24868,7 @@
         <v>4151</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A220" s="11" t="s">
         <v>241</v>
       </c>
@@ -24901,7 +24900,7 @@
         <v>18982</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="221" ht="30" customHeight="1" thickBot="1" ns3:dyDescent="0.35">
       <c r="A221" s="64" t="s">
         <v>133</v>
       </c>
@@ -24915,7 +24914,7 @@
       <c r="I221" s="64"/>
       <c r="J221" s="64"/>
     </row>
-    <row r="222" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="222" ht="15.75" customHeight="1" thickTop="1" ns3:dyDescent="0.25">
       <c r="A222" s="70" t="s">
         <v>82</v>
       </c>
@@ -24929,7 +24928,7 @@
       <c r="I222" s="70"/>
       <c r="J222" s="70"/>
     </row>
-    <row r="223" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A223" s="63" t="s">
         <v>173</v>
       </c>
@@ -24943,7 +24942,7 @@
       <c r="I223" s="63"/>
       <c r="J223" s="63"/>
     </row>
-    <row r="224" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A224" s="63" t="s">
         <v>135</v>
       </c>
@@ -24957,7 +24956,7 @@
       <c r="I224" s="63"/>
       <c r="J224" s="63"/>
     </row>
-    <row r="225" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A225" s="63" t="s">
         <v>62</v>
       </c>
@@ -24971,7 +24970,7 @@
       <c r="I225" s="63"/>
       <c r="J225" s="63"/>
     </row>
-    <row r="226" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A226" s="63" t="s">
         <v>161</v>
       </c>
@@ -24985,7 +24984,7 @@
       <c r="I226" s="63"/>
       <c r="J226" s="63"/>
     </row>
-    <row r="227" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A227" s="63" t="s">
         <v>185</v>
       </c>
@@ -24999,7 +24998,7 @@
       <c r="I227" s="63"/>
       <c r="J227" s="63"/>
     </row>
-    <row r="228" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A228" s="63" t="s">
         <v>186</v>
       </c>
@@ -25013,7 +25012,7 @@
       <c r="I228" s="63"/>
       <c r="J228" s="63"/>
     </row>
-    <row r="229" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" ht="31.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A229" s="69" t="s">
         <v>168</v>
       </c>
@@ -25027,7 +25026,7 @@
       <c r="I229" s="69"/>
       <c r="J229" s="69"/>
     </row>
-    <row r="230" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A230" s="63" t="s">
         <v>195</v>
       </c>
@@ -25041,7 +25040,7 @@
       <c r="I230" s="63"/>
       <c r="J230" s="63"/>
     </row>
-    <row r="231" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A231" s="63" t="s">
         <v>244</v>
       </c>
@@ -25055,7 +25054,7 @@
       <c r="I231" s="63"/>
       <c r="J231" s="63"/>
     </row>
-    <row r="232" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A232" s="63" t="s">
         <v>242</v>
       </c>
@@ -25069,7 +25068,7 @@
       <c r="I232" s="63"/>
       <c r="J232" s="63"/>
     </row>
-    <row r="233" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A233" s="63" t="s">
         <v>240</v>
       </c>
@@ -25083,7 +25082,7 @@
       <c r="I233" s="63"/>
       <c r="J233" s="63"/>
     </row>
-    <row r="234" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A234" s="61" t="s">
         <v>238</v>
       </c>
@@ -25097,7 +25096,7 @@
       <c r="I234" s="61"/>
       <c r="J234" s="61"/>
     </row>
-    <row r="235" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" ht="31.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A235" s="59" t="s">
         <v>237</v>
       </c>
@@ -25111,7 +25110,7 @@
       <c r="I235" s="59"/>
       <c r="J235" s="59"/>
     </row>
-    <row r="236" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" ht="31.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A236" s="59" t="s">
         <v>236</v>
       </c>
@@ -25125,7 +25124,7 @@
       <c r="I236" s="59"/>
       <c r="J236" s="59"/>
     </row>
-    <row r="237" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" ht="31.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A237" s="59" t="s">
         <v>252</v>
       </c>
@@ -25139,7 +25138,7 @@
       <c r="I237" s="59"/>
       <c r="J237" s="59"/>
     </row>
-    <row r="238" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A238" s="62" t="s">
         <v>5</v>
       </c>
@@ -25183,7 +25182,7 @@
     <mergeCell ref="A237:J237"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A238" r:id="rId1" location="copyright-and-creative-commons" xr:uid="{C26E78A9-2BD0-4502-B496-9C5E482783E4}"/>
+    <hyperlink ref="A238" r:id="rId1" location="copyright-and-creative-commons" ns2:uid="{C26E78A9-2BD0-4502-B496-9C5E482783E4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -25192,12 +25191,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A54E1BC-3885-44D1-AB08-19661EA8120F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{3A54E1BC-3885-44D1-AB08-19661EA8120F}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:J89"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5" customWidth="1"/>
     <col min="2" max="3" width="16.25" customWidth="1"/>
@@ -25207,10 +25206,9 @@
     <col min="7" max="7" width="11.25" customWidth="1"/>
     <col min="8" max="8" width="15.125" customWidth="1"/>
     <col min="9" max="10" width="11.25" customWidth="1"/>
-    <col min="11" max="16384" width="8.625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="65.25" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="66" t="s">
         <v>245</v>
       </c>
@@ -25224,7 +25222,7 @@
       <c r="I1" s="66"/>
       <c r="J1" s="66"/>
     </row>
-    <row r="2" spans="1:10" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="36" customHeight="1" thickBot="1" ns3:dyDescent="0.35">
       <c r="A2" s="71" t="s">
         <v>179</v>
       </c>
@@ -25238,7 +25236,7 @@
       <c r="I2" s="71"/>
       <c r="J2" s="71"/>
     </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15.75" customHeight="1" thickTop="1" ns3:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>83</v>
       </c>
@@ -25252,8 +25250,8 @@
       <c r="I3" s="58"/>
       <c r="J3" s="58"/>
     </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:10" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.75" customHeight="1" ns3:dyDescent="0.25"/>
+    <row r="5" ht="64.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>64</v>
       </c>
@@ -25285,7 +25283,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="67" t="s">
         <v>87</v>
@@ -25299,7 +25297,7 @@
       <c r="I6" s="67"/>
       <c r="J6" s="67"/>
     </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -25313,7 +25311,7 @@
       <c r="I7" s="36"/>
       <c r="J7" s="36"/>
     </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>27</v>
       </c>
@@ -25345,7 +25343,7 @@
         <v>28664</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>8</v>
       </c>
@@ -25377,7 +25375,7 @@
         <v>44223</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>9</v>
       </c>
@@ -25409,7 +25407,7 @@
         <v>45260</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>10</v>
       </c>
@@ -25441,7 +25439,7 @@
         <v>47607</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>11</v>
       </c>
@@ -25473,7 +25471,7 @@
         <v>43997</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>12</v>
       </c>
@@ -25505,7 +25503,7 @@
         <v>39767</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>13</v>
       </c>
@@ -25537,7 +25535,7 @@
         <v>30628</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>14</v>
       </c>
@@ -25569,7 +25567,7 @@
         <v>23734</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>28</v>
       </c>
@@ -25601,7 +25599,7 @@
         <v>33912</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A17" s="27" t="s">
         <v>74</v>
       </c>
@@ -25633,7 +25631,7 @@
         <v>339462</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B18" s="36"/>
       <c r="C18" s="36"/>
       <c r="D18" s="36"/>
@@ -25644,7 +25642,7 @@
       <c r="I18" s="36"/>
       <c r="J18" s="36"/>
     </row>
-    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -25658,7 +25656,7 @@
       <c r="I19" s="36"/>
       <c r="J19" s="36"/>
     </row>
-    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>27</v>
       </c>
@@ -25690,7 +25688,7 @@
         <v>8954</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>8</v>
       </c>
@@ -25722,7 +25720,7 @@
         <v>13568</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>9</v>
       </c>
@@ -25754,7 +25752,7 @@
         <v>14486</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>10</v>
       </c>
@@ -25786,7 +25784,7 @@
         <v>15538</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>11</v>
       </c>
@@ -25818,7 +25816,7 @@
         <v>15065</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>12</v>
       </c>
@@ -25850,7 +25848,7 @@
         <v>12761</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>13</v>
       </c>
@@ -25882,7 +25880,7 @@
         <v>9401</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>14</v>
       </c>
@@ -25914,7 +25912,7 @@
         <v>6893</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>28</v>
       </c>
@@ -25946,7 +25944,7 @@
         <v>8064</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A29" s="27" t="s">
         <v>74</v>
       </c>
@@ -25978,7 +25976,7 @@
         <v>105702</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B30" s="36"/>
       <c r="C30" s="36"/>
       <c r="D30" s="36"/>
@@ -25989,7 +25987,7 @@
       <c r="I30" s="36"/>
       <c r="J30" s="36"/>
     </row>
-    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A31" t="s">
         <v>77</v>
       </c>
@@ -26003,7 +26001,7 @@
       <c r="I31" s="36"/>
       <c r="J31" s="36"/>
     </row>
-    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>27</v>
       </c>
@@ -26035,7 +26033,7 @@
         <v>37811</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>8</v>
       </c>
@@ -26067,7 +26065,7 @@
         <v>57981</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>9</v>
       </c>
@@ -26099,7 +26097,7 @@
         <v>59927</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>10</v>
       </c>
@@ -26131,7 +26129,7 @@
         <v>63287</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>11</v>
       </c>
@@ -26163,7 +26161,7 @@
         <v>59223</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>12</v>
       </c>
@@ -26195,7 +26193,7 @@
         <v>52660</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>13</v>
       </c>
@@ -26227,7 +26225,7 @@
         <v>40150</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>14</v>
       </c>
@@ -26259,7 +26257,7 @@
         <v>30717</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>28</v>
       </c>
@@ -26291,7 +26289,7 @@
         <v>42182</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A41" s="27" t="s">
         <v>74</v>
       </c>
@@ -26323,7 +26321,7 @@
         <v>446718</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B42" s="36"/>
       <c r="C42" s="36"/>
       <c r="D42" s="36"/>
@@ -26334,7 +26332,7 @@
       <c r="I42" s="36"/>
       <c r="J42" s="36"/>
     </row>
-    <row r="43" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A43" t="s">
         <v>26</v>
       </c>
@@ -26366,7 +26364,7 @@
         <v>4326</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>66</v>
       </c>
@@ -26398,7 +26396,7 @@
         <v>451045</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A45" s="9"/>
       <c r="B45" s="67" t="s">
         <v>63</v>
@@ -26412,7 +26410,7 @@
       <c r="I45" s="67"/>
       <c r="J45" s="67"/>
     </row>
-    <row r="46" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -26426,7 +26424,7 @@
       <c r="I46" s="36"/>
       <c r="J46" s="36"/>
     </row>
-    <row r="47" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>27</v>
       </c>
@@ -26458,7 +26456,7 @@
         <v>29039</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>8</v>
       </c>
@@ -26490,7 +26488,7 @@
         <v>43703</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>9</v>
       </c>
@@ -26522,7 +26520,7 @@
         <v>45573</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>10</v>
       </c>
@@ -26554,7 +26552,7 @@
         <v>46575</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>11</v>
       </c>
@@ -26586,7 +26584,7 @@
         <v>43310</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A52" s="10" t="s">
         <v>12</v>
       </c>
@@ -26618,7 +26616,7 @@
         <v>39337</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>13</v>
       </c>
@@ -26650,7 +26648,7 @@
         <v>29541</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A54" s="10" t="s">
         <v>14</v>
       </c>
@@ -26682,7 +26680,7 @@
         <v>22928</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>28</v>
       </c>
@@ -26714,7 +26712,7 @@
         <v>32368</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A56" s="27" t="s">
         <v>74</v>
       </c>
@@ -26746,7 +26744,7 @@
         <v>334190</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B57" s="36"/>
       <c r="C57" s="36"/>
       <c r="D57" s="36"/>
@@ -26757,7 +26755,7 @@
       <c r="I57" s="36"/>
       <c r="J57" s="36"/>
     </row>
-    <row r="58" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -26771,7 +26769,7 @@
       <c r="I58" s="36"/>
       <c r="J58" s="36"/>
     </row>
-    <row r="59" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>27</v>
       </c>
@@ -26803,7 +26801,7 @@
         <v>9228</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>8</v>
       </c>
@@ -26835,7 +26833,7 @@
         <v>13924</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A61" s="10" t="s">
         <v>9</v>
       </c>
@@ -26867,7 +26865,7 @@
         <v>15054</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A62" s="10" t="s">
         <v>10</v>
       </c>
@@ -26899,7 +26897,7 @@
         <v>15913</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A63" s="10" t="s">
         <v>11</v>
       </c>
@@ -26931,7 +26929,7 @@
         <v>14932</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A64" s="10" t="s">
         <v>12</v>
       </c>
@@ -26963,7 +26961,7 @@
         <v>12876</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A65" s="10" t="s">
         <v>13</v>
       </c>
@@ -26995,7 +26993,7 @@
         <v>9375</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A66" s="10" t="s">
         <v>14</v>
       </c>
@@ -27027,7 +27025,7 @@
         <v>6795</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A67" s="10" t="s">
         <v>28</v>
       </c>
@@ -27059,7 +27057,7 @@
         <v>7846</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A68" s="27" t="s">
         <v>74</v>
       </c>
@@ -27091,7 +27089,7 @@
         <v>107125</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B69" s="36"/>
       <c r="C69" s="36"/>
       <c r="D69" s="36"/>
@@ -27102,7 +27100,7 @@
       <c r="I69" s="36"/>
       <c r="J69" s="36"/>
     </row>
-    <row r="70" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A70" t="s">
         <v>77</v>
       </c>
@@ -27116,7 +27114,7 @@
       <c r="I70" s="36"/>
       <c r="J70" s="36"/>
     </row>
-    <row r="71" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A71" s="10" t="s">
         <v>27</v>
       </c>
@@ -27148,7 +27146,7 @@
         <v>38460</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A72" s="10" t="s">
         <v>8</v>
       </c>
@@ -27180,7 +27178,7 @@
         <v>57805</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A73" s="10" t="s">
         <v>9</v>
       </c>
@@ -27212,7 +27210,7 @@
         <v>60810</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A74" s="10" t="s">
         <v>10</v>
       </c>
@@ -27244,7 +27242,7 @@
         <v>62660</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A75" s="10" t="s">
         <v>11</v>
       </c>
@@ -27276,7 +27274,7 @@
         <v>58408</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A76" s="10" t="s">
         <v>12</v>
       </c>
@@ -27308,7 +27306,7 @@
         <v>52363</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A77" s="10" t="s">
         <v>13</v>
       </c>
@@ -27340,7 +27338,7 @@
         <v>39022</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A78" s="10" t="s">
         <v>14</v>
       </c>
@@ -27372,7 +27370,7 @@
         <v>29839</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A79" s="10" t="s">
         <v>28</v>
       </c>
@@ -27404,7 +27402,7 @@
         <v>40396</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A80" s="27" t="s">
         <v>74</v>
       </c>
@@ -27436,7 +27434,7 @@
         <v>442922</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B81" s="36"/>
       <c r="C81" s="36"/>
       <c r="D81" s="36"/>
@@ -27447,7 +27445,7 @@
       <c r="I81" s="36"/>
       <c r="J81" s="36"/>
     </row>
-    <row r="82" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A82" t="s">
         <v>26</v>
       </c>
@@ -27479,7 +27477,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A83" s="11" t="s">
         <v>66</v>
       </c>
@@ -27511,7 +27509,7 @@
         <v>447122</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" ht="30" customHeight="1" thickBot="1" ns3:dyDescent="0.35">
       <c r="A84" s="64" t="s">
         <v>133</v>
       </c>
@@ -27525,7 +27523,7 @@
       <c r="I84" s="64"/>
       <c r="J84" s="64"/>
     </row>
-    <row r="85" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="15.75" customHeight="1" thickTop="1" ns3:dyDescent="0.25">
       <c r="A85" s="70" t="s">
         <v>135</v>
       </c>
@@ -27539,7 +27537,7 @@
       <c r="I85" s="70"/>
       <c r="J85" s="70"/>
     </row>
-    <row r="86" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A86" s="63" t="s">
         <v>75</v>
       </c>
@@ -27553,7 +27551,7 @@
       <c r="I86" s="63"/>
       <c r="J86" s="63"/>
     </row>
-    <row r="87" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A87" s="63" t="s">
         <v>76</v>
       </c>
@@ -27567,7 +27565,7 @@
       <c r="I87" s="63"/>
       <c r="J87" s="63"/>
     </row>
-    <row r="88" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A88" s="63" t="s">
         <v>78</v>
       </c>
@@ -27581,7 +27579,7 @@
       <c r="I88" s="63"/>
       <c r="J88" s="63"/>
     </row>
-    <row r="89" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A89" s="62" t="s">
         <v>5</v>
       </c>
@@ -27611,7 +27609,7 @@
     <mergeCell ref="A89:J89"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A89" r:id="rId1" location="copyright-and-creative-commons" xr:uid="{01B9F520-3189-4686-8F67-D18FD3D87AF3}"/>
+    <hyperlink ref="A89" r:id="rId1" location="copyright-and-creative-commons" ns2:uid="{01B9F520-3189-4686-8F67-D18FD3D87AF3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -27620,12 +27618,12 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{902CA31D-75A5-4C6A-B859-5212144819DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{902CA31D-75A5-4C6A-B859-5212144819DC}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:J91"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5" customWidth="1"/>
     <col min="2" max="3" width="16.25" customWidth="1"/>
@@ -27635,10 +27633,9 @@
     <col min="7" max="7" width="11.25" customWidth="1"/>
     <col min="8" max="8" width="15.125" customWidth="1"/>
     <col min="9" max="10" width="11.25" customWidth="1"/>
-    <col min="11" max="16384" width="8.625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="65.25" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="66" t="s">
         <v>264</v>
       </c>
@@ -27652,7 +27649,7 @@
       <c r="I1" s="66"/>
       <c r="J1" s="66"/>
     </row>
-    <row r="2" spans="1:10" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="36" customHeight="1" thickBot="1" ns3:dyDescent="0.35">
       <c r="A2" s="71" t="s">
         <v>180</v>
       </c>
@@ -27666,7 +27663,7 @@
       <c r="I2" s="71"/>
       <c r="J2" s="71"/>
     </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15.75" customHeight="1" thickTop="1" ns3:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>83</v>
       </c>
@@ -27680,8 +27677,8 @@
       <c r="I3" s="58"/>
       <c r="J3" s="58"/>
     </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:10" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.75" customHeight="1" ns3:dyDescent="0.25"/>
+    <row r="5" ht="64.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>64</v>
       </c>
@@ -27713,7 +27710,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="67" t="s">
         <v>87</v>
@@ -27727,7 +27724,7 @@
       <c r="I6" s="67"/>
       <c r="J6" s="67"/>
     </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -27741,7 +27738,7 @@
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
     </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>27</v>
       </c>
@@ -27773,7 +27770,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>8</v>
       </c>
@@ -27805,7 +27802,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>9</v>
       </c>
@@ -27837,7 +27834,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>10</v>
       </c>
@@ -27869,7 +27866,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>11</v>
       </c>
@@ -27901,7 +27898,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>12</v>
       </c>
@@ -27933,7 +27930,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>13</v>
       </c>
@@ -27965,7 +27962,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>14</v>
       </c>
@@ -27997,7 +27994,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>28</v>
       </c>
@@ -28029,7 +28026,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A17" s="27" t="s">
         <v>260</v>
       </c>
@@ -28061,7 +28058,7 @@
         <v>11052</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B18" s="41"/>
       <c r="C18" s="41"/>
       <c r="D18" s="41"/>
@@ -28072,7 +28069,7 @@
       <c r="I18" s="41"/>
       <c r="J18" s="41"/>
     </row>
-    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -28086,7 +28083,7 @@
       <c r="I19" s="41"/>
       <c r="J19" s="41"/>
     </row>
-    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>27</v>
       </c>
@@ -28118,7 +28115,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>8</v>
       </c>
@@ -28150,7 +28147,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>9</v>
       </c>
@@ -28182,7 +28179,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>10</v>
       </c>
@@ -28214,7 +28211,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>11</v>
       </c>
@@ -28246,7 +28243,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>12</v>
       </c>
@@ -28278,7 +28275,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>13</v>
       </c>
@@ -28310,7 +28307,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>14</v>
       </c>
@@ -28342,7 +28339,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>28</v>
       </c>
@@ -28374,7 +28371,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A29" s="27" t="s">
         <v>260</v>
       </c>
@@ -28406,7 +28403,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B30" s="41"/>
       <c r="C30" s="41"/>
       <c r="D30" s="41"/>
@@ -28417,7 +28414,7 @@
       <c r="I30" s="41"/>
       <c r="J30" s="41"/>
     </row>
-    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A31" t="s">
         <v>258</v>
       </c>
@@ -28431,7 +28428,7 @@
       <c r="I31" s="41"/>
       <c r="J31" s="41"/>
     </row>
-    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>27</v>
       </c>
@@ -28463,7 +28460,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>8</v>
       </c>
@@ -28495,7 +28492,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>9</v>
       </c>
@@ -28527,7 +28524,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>10</v>
       </c>
@@ -28559,7 +28556,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>11</v>
       </c>
@@ -28591,7 +28588,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>12</v>
       </c>
@@ -28623,7 +28620,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>13</v>
       </c>
@@ -28655,7 +28652,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>14</v>
       </c>
@@ -28687,7 +28684,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>28</v>
       </c>
@@ -28719,7 +28716,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A41" s="27" t="s">
         <v>260</v>
       </c>
@@ -28751,7 +28748,7 @@
         <v>12698</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B42" s="41"/>
       <c r="C42" s="41"/>
       <c r="D42" s="41"/>
@@ -28762,7 +28759,7 @@
       <c r="I42" s="41"/>
       <c r="J42" s="41"/>
     </row>
-    <row r="43" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A43" t="s">
         <v>26</v>
       </c>
@@ -28794,7 +28791,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>66</v>
       </c>
@@ -28826,7 +28823,7 @@
         <v>12748</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A45" s="9"/>
       <c r="B45" s="67" t="s">
         <v>63</v>
@@ -28840,7 +28837,7 @@
       <c r="I45" s="67"/>
       <c r="J45" s="67"/>
     </row>
-    <row r="46" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -28854,7 +28851,7 @@
       <c r="I46" s="23"/>
       <c r="J46" s="23"/>
     </row>
-    <row r="47" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>27</v>
       </c>
@@ -28886,7 +28883,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>8</v>
       </c>
@@ -28918,7 +28915,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>9</v>
       </c>
@@ -28950,7 +28947,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>10</v>
       </c>
@@ -28982,7 +28979,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>11</v>
       </c>
@@ -29014,7 +29011,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A52" s="10" t="s">
         <v>12</v>
       </c>
@@ -29046,7 +29043,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>13</v>
       </c>
@@ -29078,7 +29075,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A54" s="10" t="s">
         <v>14</v>
       </c>
@@ -29110,7 +29107,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>28</v>
       </c>
@@ -29142,7 +29139,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A56" s="27" t="s">
         <v>260</v>
       </c>
@@ -29174,7 +29171,7 @@
         <v>11035</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>
@@ -29185,7 +29182,7 @@
       <c r="I57" s="14"/>
       <c r="J57" s="14"/>
     </row>
-    <row r="58" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -29199,7 +29196,7 @@
       <c r="I58" s="14"/>
       <c r="J58" s="14"/>
     </row>
-    <row r="59" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>27</v>
       </c>
@@ -29231,7 +29228,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>8</v>
       </c>
@@ -29263,7 +29260,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A61" s="10" t="s">
         <v>9</v>
       </c>
@@ -29295,7 +29292,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A62" s="10" t="s">
         <v>10</v>
       </c>
@@ -29327,7 +29324,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A63" s="10" t="s">
         <v>11</v>
       </c>
@@ -29359,7 +29356,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A64" s="10" t="s">
         <v>12</v>
       </c>
@@ -29391,7 +29388,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A65" s="10" t="s">
         <v>13</v>
       </c>
@@ -29423,7 +29420,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A66" s="10" t="s">
         <v>14</v>
       </c>
@@ -29455,7 +29452,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A67" s="10" t="s">
         <v>28</v>
       </c>
@@ -29487,7 +29484,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A68" s="27" t="s">
         <v>260</v>
       </c>
@@ -29519,7 +29516,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
@@ -29530,7 +29527,7 @@
       <c r="I69" s="14"/>
       <c r="J69" s="14"/>
     </row>
-    <row r="70" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A70" t="s">
         <v>258</v>
       </c>
@@ -29544,7 +29541,7 @@
       <c r="I70" s="14"/>
       <c r="J70" s="14"/>
     </row>
-    <row r="71" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A71" s="10" t="s">
         <v>27</v>
       </c>
@@ -29576,7 +29573,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A72" s="10" t="s">
         <v>8</v>
       </c>
@@ -29608,7 +29605,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A73" s="10" t="s">
         <v>9</v>
       </c>
@@ -29640,7 +29637,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A74" s="10" t="s">
         <v>10</v>
       </c>
@@ -29672,7 +29669,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A75" s="10" t="s">
         <v>11</v>
       </c>
@@ -29704,7 +29701,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A76" s="10" t="s">
         <v>12</v>
       </c>
@@ -29736,7 +29733,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A77" s="10" t="s">
         <v>13</v>
       </c>
@@ -29768,7 +29765,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A78" s="10" t="s">
         <v>14</v>
       </c>
@@ -29800,7 +29797,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A79" s="10" t="s">
         <v>28</v>
       </c>
@@ -29832,7 +29829,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A80" s="27" t="s">
         <v>260</v>
       </c>
@@ -29864,7 +29861,7 @@
         <v>12703</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
       <c r="D81" s="14"/>
@@ -29875,7 +29872,7 @@
       <c r="I81" s="14"/>
       <c r="J81" s="14"/>
     </row>
-    <row r="82" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A82" t="s">
         <v>26</v>
       </c>
@@ -29907,7 +29904,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A83" s="11" t="s">
         <v>66</v>
       </c>
@@ -29939,7 +29936,7 @@
         <v>12763</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" ht="30" customHeight="1" thickBot="1" ns3:dyDescent="0.35">
       <c r="A84" s="64" t="s">
         <v>133</v>
       </c>
@@ -29953,7 +29950,7 @@
       <c r="I84" s="64"/>
       <c r="J84" s="64"/>
     </row>
-    <row r="85" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="15.75" customHeight="1" thickTop="1" ns3:dyDescent="0.25">
       <c r="A85" s="70" t="s">
         <v>173</v>
       </c>
@@ -29967,7 +29964,7 @@
       <c r="I85" s="70"/>
       <c r="J85" s="70"/>
     </row>
-    <row r="86" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A86" s="58" t="s">
         <v>135</v>
       </c>
@@ -29981,7 +29978,7 @@
       <c r="I86" s="58"/>
       <c r="J86" s="58"/>
     </row>
-    <row r="87" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="31.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A87" s="69" t="s">
         <v>256</v>
       </c>
@@ -29995,7 +29992,7 @@
       <c r="I87" s="69"/>
       <c r="J87" s="69"/>
     </row>
-    <row r="88" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A88" s="63" t="s">
         <v>261</v>
       </c>
@@ -30009,7 +30006,7 @@
       <c r="I88" s="63"/>
       <c r="J88" s="63"/>
     </row>
-    <row r="89" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A89" s="63" t="s">
         <v>259</v>
       </c>
@@ -30023,7 +30020,7 @@
       <c r="I89" s="63"/>
       <c r="J89" s="63"/>
     </row>
-    <row r="90" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A90" s="63" t="s">
         <v>257</v>
       </c>
@@ -30037,7 +30034,7 @@
       <c r="I90" s="63"/>
       <c r="J90" s="63"/>
     </row>
-    <row r="91" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A91" s="62" t="s">
         <v>5</v>
       </c>
@@ -30069,7 +30066,7 @@
     <mergeCell ref="A89:J89"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A91" r:id="rId1" location="copyright-and-creative-commons" xr:uid="{ACE96EB0-223C-4117-8976-62A934BA3C1C}"/>
+    <hyperlink ref="A91" r:id="rId1" location="copyright-and-creative-commons" ns2:uid="{ACE96EB0-223C-4117-8976-62A934BA3C1C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -30078,12 +30075,12 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32421C52-E5CA-45BA-B7BE-EC219C6E580A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{32421C52-E5CA-45BA-B7BE-EC219C6E580A}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:J89"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5" customWidth="1"/>
     <col min="2" max="3" width="16.25" customWidth="1"/>
@@ -30093,10 +30090,9 @@
     <col min="7" max="7" width="11.25" customWidth="1"/>
     <col min="8" max="8" width="15.125" customWidth="1"/>
     <col min="9" max="10" width="11.25" customWidth="1"/>
-    <col min="11" max="16384" width="8.625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="65.25" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="66" t="s">
         <v>246</v>
       </c>
@@ -30110,7 +30106,7 @@
       <c r="I1" s="66"/>
       <c r="J1" s="66"/>
     </row>
-    <row r="2" spans="1:10" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="36" customHeight="1" thickBot="1" ns3:dyDescent="0.35">
       <c r="A2" s="71" t="s">
         <v>181</v>
       </c>
@@ -30124,7 +30120,7 @@
       <c r="I2" s="71"/>
       <c r="J2" s="71"/>
     </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15.75" customHeight="1" thickTop="1" ns3:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>83</v>
       </c>
@@ -30138,8 +30134,8 @@
       <c r="I3" s="58"/>
       <c r="J3" s="58"/>
     </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:10" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.75" customHeight="1" ns3:dyDescent="0.25"/>
+    <row r="5" ht="64.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>64</v>
       </c>
@@ -30171,7 +30167,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="67" t="s">
         <v>87</v>
@@ -30185,7 +30181,7 @@
       <c r="I6" s="67"/>
       <c r="J6" s="67"/>
     </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -30199,7 +30195,7 @@
       <c r="I7" s="41"/>
       <c r="J7" s="41"/>
     </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>27</v>
       </c>
@@ -30231,7 +30227,7 @@
         <v>14306</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>8</v>
       </c>
@@ -30263,7 +30259,7 @@
         <v>42612</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>9</v>
       </c>
@@ -30295,7 +30291,7 @@
         <v>43542</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>10</v>
       </c>
@@ -30327,7 +30323,7 @@
         <v>45727</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>11</v>
       </c>
@@ -30359,7 +30355,7 @@
         <v>42337</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>12</v>
       </c>
@@ -30391,7 +30387,7 @@
         <v>38506</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>13</v>
       </c>
@@ -30423,7 +30419,7 @@
         <v>29715</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>14</v>
       </c>
@@ -30455,7 +30451,7 @@
         <v>23065</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>28</v>
       </c>
@@ -30487,7 +30483,7 @@
         <v>32808</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A17" s="27" t="s">
         <v>74</v>
       </c>
@@ -30519,7 +30515,7 @@
         <v>314291</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B18" s="41"/>
       <c r="C18" s="41"/>
       <c r="D18" s="41"/>
@@ -30530,7 +30526,7 @@
       <c r="I18" s="41"/>
       <c r="J18" s="41"/>
     </row>
-    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -30544,7 +30540,7 @@
       <c r="I19" s="41"/>
       <c r="J19" s="41"/>
     </row>
-    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>27</v>
       </c>
@@ -30576,7 +30572,7 @@
         <v>4234</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>8</v>
       </c>
@@ -30608,7 +30604,7 @@
         <v>13334</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>9</v>
       </c>
@@ -30640,7 +30636,7 @@
         <v>14214</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>10</v>
       </c>
@@ -30672,7 +30668,7 @@
         <v>15237</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>11</v>
       </c>
@@ -30704,7 +30700,7 @@
         <v>14797</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>12</v>
       </c>
@@ -30736,7 +30732,7 @@
         <v>12567</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>13</v>
       </c>
@@ -30768,7 +30764,7 @@
         <v>9249</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>14</v>
       </c>
@@ -30800,7 +30796,7 @@
         <v>6805</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>28</v>
       </c>
@@ -30832,7 +30828,7 @@
         <v>7959</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A29" s="27" t="s">
         <v>74</v>
       </c>
@@ -30864,7 +30860,7 @@
         <v>99371</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B30" s="41"/>
       <c r="C30" s="41"/>
       <c r="D30" s="41"/>
@@ -30875,7 +30871,7 @@
       <c r="I30" s="41"/>
       <c r="J30" s="41"/>
     </row>
-    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A31" t="s">
         <v>77</v>
       </c>
@@ -30889,7 +30885,7 @@
       <c r="I31" s="41"/>
       <c r="J31" s="41"/>
     </row>
-    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>27</v>
       </c>
@@ -30921,7 +30917,7 @@
         <v>18601</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>8</v>
       </c>
@@ -30953,7 +30949,7 @@
         <v>56132</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>9</v>
       </c>
@@ -30985,7 +30981,7 @@
         <v>57932</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>10</v>
       </c>
@@ -31017,7 +31013,7 @@
         <v>61106</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>11</v>
       </c>
@@ -31049,7 +31045,7 @@
         <v>57298</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>12</v>
       </c>
@@ -31081,7 +31077,7 @@
         <v>51196</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>13</v>
       </c>
@@ -31113,7 +31109,7 @@
         <v>39083</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>14</v>
       </c>
@@ -31145,7 +31141,7 @@
         <v>29960</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>28</v>
       </c>
@@ -31177,7 +31173,7 @@
         <v>40971</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A41" s="27" t="s">
         <v>74</v>
       </c>
@@ -31209,7 +31205,7 @@
         <v>415045</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B42" s="41"/>
       <c r="C42" s="41"/>
       <c r="D42" s="41"/>
@@ -31220,7 +31216,7 @@
       <c r="I42" s="41"/>
       <c r="J42" s="41"/>
     </row>
-    <row r="43" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A43" t="s">
         <v>26</v>
       </c>
@@ -31252,7 +31248,7 @@
         <v>4271</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>66</v>
       </c>
@@ -31284,7 +31280,7 @@
         <v>419318</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A45" s="9"/>
       <c r="B45" s="67" t="s">
         <v>63</v>
@@ -31298,7 +31294,7 @@
       <c r="I45" s="67"/>
       <c r="J45" s="67"/>
     </row>
-    <row r="46" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -31312,7 +31308,7 @@
       <c r="I46" s="41"/>
       <c r="J46" s="41"/>
     </row>
-    <row r="47" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>27</v>
       </c>
@@ -31344,7 +31340,7 @@
         <v>14208</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>8</v>
       </c>
@@ -31376,7 +31372,7 @@
         <v>41961</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>9</v>
       </c>
@@ -31408,7 +31404,7 @@
         <v>43810</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>10</v>
       </c>
@@ -31440,7 +31436,7 @@
         <v>44670</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>11</v>
       </c>
@@ -31472,7 +31468,7 @@
         <v>41741</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A52" s="10" t="s">
         <v>12</v>
       </c>
@@ -31504,7 +31500,7 @@
         <v>38057</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>13</v>
       </c>
@@ -31536,7 +31532,7 @@
         <v>28648</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A54" s="10" t="s">
         <v>14</v>
       </c>
@@ -31568,7 +31564,7 @@
         <v>22326</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>28</v>
       </c>
@@ -31600,7 +31596,7 @@
         <v>31317</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A56" s="27" t="s">
         <v>74</v>
       </c>
@@ -31632,7 +31628,7 @@
         <v>308532</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B57" s="41"/>
       <c r="C57" s="41"/>
       <c r="D57" s="41"/>
@@ -31643,7 +31639,7 @@
       <c r="I57" s="41"/>
       <c r="J57" s="41"/>
     </row>
-    <row r="58" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -31657,7 +31653,7 @@
       <c r="I58" s="41"/>
       <c r="J58" s="41"/>
     </row>
-    <row r="59" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>27</v>
       </c>
@@ -31689,7 +31685,7 @@
         <v>4160</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>8</v>
       </c>
@@ -31721,7 +31717,7 @@
         <v>13682</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A61" s="10" t="s">
         <v>9</v>
       </c>
@@ -31753,7 +31749,7 @@
         <v>14791</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A62" s="10" t="s">
         <v>10</v>
       </c>
@@ -31785,7 +31781,7 @@
         <v>15640</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A63" s="10" t="s">
         <v>11</v>
       </c>
@@ -31817,7 +31813,7 @@
         <v>14646</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A64" s="10" t="s">
         <v>12</v>
       </c>
@@ -31849,7 +31845,7 @@
         <v>12666</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A65" s="10" t="s">
         <v>13</v>
       </c>
@@ -31881,7 +31877,7 @@
         <v>9254</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A66" s="10" t="s">
         <v>14</v>
       </c>
@@ -31913,7 +31909,7 @@
         <v>6673</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A67" s="10" t="s">
         <v>28</v>
       </c>
@@ -31945,7 +31941,7 @@
         <v>7739</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A68" s="27" t="s">
         <v>74</v>
       </c>
@@ -31977,7 +31973,7 @@
         <v>100425</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B69" s="41"/>
       <c r="C69" s="41"/>
       <c r="D69" s="41"/>
@@ -31988,7 +31984,7 @@
       <c r="I69" s="41"/>
       <c r="J69" s="41"/>
     </row>
-    <row r="70" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A70" t="s">
         <v>77</v>
       </c>
@@ -32002,7 +31998,7 @@
       <c r="I70" s="41"/>
       <c r="J70" s="41"/>
     </row>
-    <row r="71" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A71" s="10" t="s">
         <v>27</v>
       </c>
@@ -32034,7 +32030,7 @@
         <v>18428</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A72" s="10" t="s">
         <v>8</v>
       </c>
@@ -32066,7 +32062,7 @@
         <v>55820</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A73" s="10" t="s">
         <v>9</v>
       </c>
@@ -32098,7 +32094,7 @@
         <v>58781</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A74" s="10" t="s">
         <v>10</v>
       </c>
@@ -32130,7 +32126,7 @@
         <v>60478</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A75" s="10" t="s">
         <v>11</v>
       </c>
@@ -32162,7 +32158,7 @@
         <v>56546</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A76" s="10" t="s">
         <v>12</v>
       </c>
@@ -32194,7 +32190,7 @@
         <v>50871</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A77" s="10" t="s">
         <v>13</v>
       </c>
@@ -32226,7 +32222,7 @@
         <v>38002</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A78" s="10" t="s">
         <v>14</v>
       </c>
@@ -32258,7 +32254,7 @@
         <v>29110</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A79" s="10" t="s">
         <v>28</v>
       </c>
@@ -32290,7 +32286,7 @@
         <v>39243</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A80" s="27" t="s">
         <v>74</v>
       </c>
@@ -32322,7 +32318,7 @@
         <v>410436</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B81" s="41"/>
       <c r="C81" s="41"/>
       <c r="D81" s="41"/>
@@ -32333,7 +32329,7 @@
       <c r="I81" s="41"/>
       <c r="J81" s="41"/>
     </row>
-    <row r="82" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A82" t="s">
         <v>26</v>
       </c>
@@ -32365,7 +32361,7 @@
         <v>4144</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A83" s="11" t="s">
         <v>66</v>
       </c>
@@ -32397,7 +32393,7 @@
         <v>414586</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" ht="30" customHeight="1" thickBot="1" ns3:dyDescent="0.35">
       <c r="A84" s="64" t="s">
         <v>133</v>
       </c>
@@ -32411,7 +32407,7 @@
       <c r="I84" s="64"/>
       <c r="J84" s="64"/>
     </row>
-    <row r="85" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="15.75" customHeight="1" thickTop="1" ns3:dyDescent="0.25">
       <c r="A85" s="70" t="s">
         <v>135</v>
       </c>
@@ -32425,7 +32421,7 @@
       <c r="I85" s="70"/>
       <c r="J85" s="70"/>
     </row>
-    <row r="86" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A86" s="63" t="s">
         <v>75</v>
       </c>
@@ -32439,7 +32435,7 @@
       <c r="I86" s="63"/>
       <c r="J86" s="63"/>
     </row>
-    <row r="87" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A87" s="63" t="s">
         <v>76</v>
       </c>
@@ -32453,7 +32449,7 @@
       <c r="I87" s="63"/>
       <c r="J87" s="63"/>
     </row>
-    <row r="88" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A88" s="63" t="s">
         <v>78</v>
       </c>
@@ -32467,7 +32463,7 @@
       <c r="I88" s="63"/>
       <c r="J88" s="63"/>
     </row>
-    <row r="89" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A89" s="62" t="s">
         <v>5</v>
       </c>
@@ -32497,7 +32493,7 @@
     <mergeCell ref="A89:J89"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A89" r:id="rId1" location="copyright-and-creative-commons" xr:uid="{76351172-37A4-462A-B259-E3E1B69B0DFC}"/>
+    <hyperlink ref="A89" r:id="rId1" location="copyright-and-creative-commons" ns2:uid="{76351172-37A4-462A-B259-E3E1B69B0DFC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -32506,12 +32502,12 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{678A1961-CF94-4AF7-97E2-156E1214ED94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{678A1961-CF94-4AF7-97E2-156E1214ED94}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:J53"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5" customWidth="1"/>
     <col min="2" max="3" width="16.25" customWidth="1"/>
@@ -32521,10 +32517,9 @@
     <col min="7" max="7" width="11.25" customWidth="1"/>
     <col min="8" max="8" width="15.125" customWidth="1"/>
     <col min="9" max="10" width="11.25" customWidth="1"/>
-    <col min="11" max="16384" width="8.625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="65.25" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="66" t="s">
         <v>247</v>
       </c>
@@ -32538,7 +32533,7 @@
       <c r="I1" s="66"/>
       <c r="J1" s="66"/>
     </row>
-    <row r="2" spans="1:10" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="36" customHeight="1" thickBot="1" ns3:dyDescent="0.35">
       <c r="A2" s="71" t="s">
         <v>182</v>
       </c>
@@ -32552,7 +32547,7 @@
       <c r="I2" s="71"/>
       <c r="J2" s="71"/>
     </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15.75" customHeight="1" thickTop="1" ns3:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>83</v>
       </c>
@@ -32566,8 +32561,8 @@
       <c r="I3" s="58"/>
       <c r="J3" s="58"/>
     </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:10" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.75" customHeight="1" ns3:dyDescent="0.25"/>
+    <row r="5" ht="64.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>64</v>
       </c>
@@ -32599,7 +32594,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="67" t="s">
         <v>87</v>
@@ -32613,7 +32608,7 @@
       <c r="I6" s="67"/>
       <c r="J6" s="67"/>
     </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -32627,7 +32622,7 @@
       <c r="I7" s="41"/>
       <c r="J7" s="41"/>
     </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>67</v>
       </c>
@@ -32659,7 +32654,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>68</v>
       </c>
@@ -32691,7 +32686,7 @@
         <v>11952</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>8</v>
       </c>
@@ -32723,7 +32718,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>53</v>
       </c>
@@ -32755,7 +32750,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A12" s="27" t="s">
         <v>74</v>
       </c>
@@ -32787,7 +32782,7 @@
         <v>14122</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B13" s="41"/>
       <c r="C13" s="41"/>
       <c r="D13" s="41"/>
@@ -32798,7 +32793,7 @@
       <c r="I13" s="41"/>
       <c r="J13" s="41"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -32812,7 +32807,7 @@
       <c r="I14" s="41"/>
       <c r="J14" s="41"/>
     </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>67</v>
       </c>
@@ -32844,7 +32839,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>68</v>
       </c>
@@ -32876,7 +32871,7 @@
         <v>3766</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>8</v>
       </c>
@@ -32908,7 +32903,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>53</v>
       </c>
@@ -32940,7 +32935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A19" s="27" t="s">
         <v>74</v>
       </c>
@@ -32972,7 +32967,7 @@
         <v>4721</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B20" s="41"/>
       <c r="C20" s="41"/>
       <c r="D20" s="41"/>
@@ -32983,7 +32978,7 @@
       <c r="I20" s="41"/>
       <c r="J20" s="41"/>
     </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A21" t="s">
         <v>77</v>
       </c>
@@ -32997,7 +32992,7 @@
       <c r="I21" s="41"/>
       <c r="J21" s="41"/>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>67</v>
       </c>
@@ -33029,7 +33024,7 @@
         <v>3025</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>68</v>
       </c>
@@ -33061,7 +33056,7 @@
         <v>15827</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>8</v>
       </c>
@@ -33093,7 +33088,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>53</v>
       </c>
@@ -33125,7 +33120,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A26" s="27" t="s">
         <v>74</v>
       </c>
@@ -33157,7 +33152,7 @@
         <v>18982</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A27" s="9"/>
       <c r="B27" s="67" t="s">
         <v>63</v>
@@ -33171,7 +33166,7 @@
       <c r="I27" s="67"/>
       <c r="J27" s="67"/>
     </row>
-    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -33185,7 +33180,7 @@
       <c r="I28" s="41"/>
       <c r="J28" s="41"/>
     </row>
-    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>67</v>
       </c>
@@ -33217,7 +33212,7 @@
         <v>2424</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>68</v>
       </c>
@@ -33249,7 +33244,7 @@
         <v>12061</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>8</v>
       </c>
@@ -33281,7 +33276,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>53</v>
       </c>
@@ -33313,7 +33308,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A33" s="27" t="s">
         <v>74</v>
       </c>
@@ -33345,7 +33340,7 @@
         <v>14614</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B34" s="41"/>
       <c r="C34" s="41"/>
       <c r="D34" s="41"/>
@@ -33356,7 +33351,7 @@
       <c r="I34" s="41"/>
       <c r="J34" s="41"/>
     </row>
-    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -33370,7 +33365,7 @@
       <c r="I35" s="41"/>
       <c r="J35" s="41"/>
     </row>
-    <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>67</v>
       </c>
@@ -33402,7 +33397,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>68</v>
       </c>
@@ -33434,7 +33429,7 @@
         <v>3874</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>8</v>
       </c>
@@ -33466,7 +33461,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>53</v>
       </c>
@@ -33498,7 +33493,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A40" s="27" t="s">
         <v>74</v>
       </c>
@@ -33530,7 +33525,7 @@
         <v>5043</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B41" s="41"/>
       <c r="C41" s="41"/>
       <c r="D41" s="41"/>
@@ -33541,7 +33536,7 @@
       <c r="I41" s="41"/>
       <c r="J41" s="41"/>
     </row>
-    <row r="42" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A42" t="s">
         <v>77</v>
       </c>
@@ -33555,7 +33550,7 @@
       <c r="I42" s="41"/>
       <c r="J42" s="41"/>
     </row>
-    <row r="43" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>67</v>
       </c>
@@ -33587,7 +33582,7 @@
         <v>3598</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>68</v>
       </c>
@@ -33619,7 +33614,7 @@
         <v>16023</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>8</v>
       </c>
@@ -33651,7 +33646,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A46" s="10" t="s">
         <v>53</v>
       </c>
@@ -33683,7 +33678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A47" s="27" t="s">
         <v>74</v>
       </c>
@@ -33715,7 +33710,7 @@
         <v>19775</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" ht="30" customHeight="1" thickBot="1" ns3:dyDescent="0.35">
       <c r="A48" s="64" t="s">
         <v>133</v>
       </c>
@@ -33729,7 +33724,7 @@
       <c r="I48" s="64"/>
       <c r="J48" s="64"/>
     </row>
-    <row r="49" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="15.75" customHeight="1" thickTop="1" ns3:dyDescent="0.25">
       <c r="A49" s="70" t="s">
         <v>135</v>
       </c>
@@ -33743,7 +33738,7 @@
       <c r="I49" s="70"/>
       <c r="J49" s="70"/>
     </row>
-    <row r="50" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A50" s="63" t="s">
         <v>75</v>
       </c>
@@ -33757,7 +33752,7 @@
       <c r="I50" s="63"/>
       <c r="J50" s="63"/>
     </row>
-    <row r="51" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A51" s="63" t="s">
         <v>76</v>
       </c>
@@ -33771,7 +33766,7 @@
       <c r="I51" s="63"/>
       <c r="J51" s="63"/>
     </row>
-    <row r="52" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A52" s="63" t="s">
         <v>78</v>
       </c>
@@ -33785,7 +33780,7 @@
       <c r="I52" s="63"/>
       <c r="J52" s="63"/>
     </row>
-    <row r="53" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A53" s="62" t="s">
         <v>5</v>
       </c>
@@ -33815,7 +33810,7 @@
     <mergeCell ref="A53:J53"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A53" r:id="rId1" location="copyright-and-creative-commons" xr:uid="{B3612303-D36D-403B-867E-11692815202A}"/>
+    <hyperlink ref="A53" r:id="rId1" location="copyright-and-creative-commons" ns2:uid="{B3612303-D36D-403B-867E-11692815202A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -33824,12 +33819,12 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85D76995-F1A6-4EEF-87FA-CF976CF8F442}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{85D76995-F1A6-4EEF-87FA-CF976CF8F442}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:J175"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.125" customWidth="1"/>
     <col min="2" max="3" width="16.25" customWidth="1"/>
@@ -33839,10 +33834,9 @@
     <col min="7" max="7" width="11.25" customWidth="1"/>
     <col min="8" max="8" width="15.125" customWidth="1"/>
     <col min="9" max="10" width="11.25" customWidth="1"/>
-    <col min="11" max="16384" width="8.625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="65.25" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="66" t="s">
         <v>268</v>
       </c>
@@ -33856,7 +33850,7 @@
       <c r="I1" s="66"/>
       <c r="J1" s="66"/>
     </row>
-    <row r="2" spans="1:10" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="36" customHeight="1" thickBot="1" ns3:dyDescent="0.35">
       <c r="A2" s="71" t="s">
         <v>234</v>
       </c>
@@ -33870,7 +33864,7 @@
       <c r="I2" s="71"/>
       <c r="J2" s="71"/>
     </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15.75" customHeight="1" thickTop="1" ns3:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>83</v>
       </c>
@@ -33884,8 +33878,8 @@
       <c r="I3" s="58"/>
       <c r="J3" s="58"/>
     </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:10" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.75" customHeight="1" ns3:dyDescent="0.25"/>
+    <row r="5" ht="64.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>162</v>
       </c>
@@ -33917,7 +33911,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="67" t="s">
         <v>87</v>
@@ -33931,7 +33925,7 @@
       <c r="I6" s="67"/>
       <c r="J6" s="67"/>
     </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -33945,7 +33939,7 @@
       <c r="I7" s="36"/>
       <c r="J7" s="36"/>
     </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>163</v>
       </c>
@@ -33977,7 +33971,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>89</v>
       </c>
@@ -34009,7 +34003,7 @@
         <v>52711</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>90</v>
       </c>
@@ -34041,7 +34035,7 @@
         <v>5517</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>164</v>
       </c>
@@ -34073,7 +34067,7 @@
         <v>16295</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>92</v>
       </c>
@@ -34105,7 +34099,7 @@
         <v>2684</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>93</v>
       </c>
@@ -34137,7 +34131,7 @@
         <v>10486</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>94</v>
       </c>
@@ -34169,7 +34163,7 @@
         <v>36251</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>95</v>
       </c>
@@ -34201,7 +34195,7 @@
         <v>8181</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>96</v>
       </c>
@@ -34233,7 +34227,7 @@
         <v>28760</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>97</v>
       </c>
@@ -34265,7 +34259,7 @@
         <v>13833</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>98</v>
       </c>
@@ -34297,7 +34291,7 @@
         <v>13640</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>99</v>
       </c>
@@ -34329,7 +34323,7 @@
         <v>18017</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>187</v>
       </c>
@@ -34361,7 +34355,7 @@
         <v>189339</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>194</v>
       </c>
@@ -34393,7 +34387,7 @@
         <v>46274</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>100</v>
       </c>
@@ -34425,7 +34419,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>101</v>
       </c>
@@ -34457,7 +34451,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>102</v>
       </c>
@@ -34489,7 +34483,7 @@
         <v>3034</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>166</v>
       </c>
@@ -34521,7 +34515,7 @@
         <v>451045</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B26" s="40"/>
       <c r="C26" s="40"/>
       <c r="D26" s="40"/>
@@ -34532,7 +34526,7 @@
       <c r="I26" s="40"/>
       <c r="J26" s="40"/>
     </row>
-    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -34546,7 +34540,7 @@
       <c r="I27" s="36"/>
       <c r="J27" s="36"/>
     </row>
-    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>163</v>
       </c>
@@ -34578,7 +34572,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>89</v>
       </c>
@@ -34610,7 +34604,7 @@
         <v>2289</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>90</v>
       </c>
@@ -34642,7 +34636,7 @@
         <v>2610</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>164</v>
       </c>
@@ -34674,7 +34668,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>92</v>
       </c>
@@ -34706,7 +34700,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>93</v>
       </c>
@@ -34738,7 +34732,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>94</v>
       </c>
@@ -34770,7 +34764,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>95</v>
       </c>
@@ -34802,7 +34796,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>96</v>
       </c>
@@ -34834,7 +34828,7 @@
         <v>2615</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>97</v>
       </c>
@@ -34866,7 +34860,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>98</v>
       </c>
@@ -34898,7 +34892,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>99</v>
       </c>
@@ -34930,7 +34924,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>187</v>
       </c>
@@ -34962,7 +34956,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A41" s="10" t="s">
         <v>194</v>
       </c>
@@ -34994,7 +34988,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>100</v>
       </c>
@@ -35026,7 +35020,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>101</v>
       </c>
@@ -35058,7 +35052,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>102</v>
       </c>
@@ -35090,7 +35084,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>166</v>
       </c>
@@ -35122,7 +35116,7 @@
         <v>12748</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B46" s="40"/>
       <c r="C46" s="40"/>
       <c r="D46" s="40"/>
@@ -35133,7 +35127,7 @@
       <c r="I46" s="40"/>
       <c r="J46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A47" t="s">
         <v>41</v>
       </c>
@@ -35147,7 +35141,7 @@
       <c r="I47" s="36"/>
       <c r="J47" s="36"/>
     </row>
-    <row r="48" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>163</v>
       </c>
@@ -35179,7 +35173,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>89</v>
       </c>
@@ -35211,7 +35205,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>90</v>
       </c>
@@ -35243,7 +35237,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>164</v>
       </c>
@@ -35275,7 +35269,7 @@
         <v>14715</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A52" s="10" t="s">
         <v>92</v>
       </c>
@@ -35307,7 +35301,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>93</v>
       </c>
@@ -35339,7 +35333,7 @@
         <v>6853</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A54" s="10" t="s">
         <v>94</v>
       </c>
@@ -35371,7 +35365,7 @@
         <v>31962</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>95</v>
       </c>
@@ -35403,7 +35397,7 @@
         <v>7515</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A56" s="10" t="s">
         <v>96</v>
       </c>
@@ -35435,7 +35429,7 @@
         <v>25705</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>97</v>
       </c>
@@ -35467,7 +35461,7 @@
         <v>12773</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A58" s="10" t="s">
         <v>98</v>
       </c>
@@ -35499,7 +35493,7 @@
         <v>12245</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>99</v>
       </c>
@@ -35531,7 +35525,7 @@
         <v>17009</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>187</v>
       </c>
@@ -35563,7 +35557,7 @@
         <v>187432</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A61" s="10" t="s">
         <v>194</v>
       </c>
@@ -35595,7 +35589,7 @@
         <v>45476</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A62" s="10" t="s">
         <v>100</v>
       </c>
@@ -35627,7 +35621,7 @@
         <v>3331</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A63" s="10" t="s">
         <v>101</v>
       </c>
@@ -35659,7 +35653,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A64" s="10" t="s">
         <v>102</v>
       </c>
@@ -35691,7 +35685,7 @@
         <v>3018</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A65" s="11" t="s">
         <v>166</v>
       </c>
@@ -35723,7 +35717,7 @@
         <v>419318</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B66" s="40"/>
       <c r="C66" s="40"/>
       <c r="D66" s="40"/>
@@ -35734,7 +35728,7 @@
       <c r="I66" s="40"/>
       <c r="J66" s="40"/>
     </row>
-    <row r="67" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A67" t="s">
         <v>42</v>
       </c>
@@ -35748,7 +35742,7 @@
       <c r="I67" s="36"/>
       <c r="J67" s="36"/>
     </row>
-    <row r="68" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A68" s="10" t="s">
         <v>163</v>
       </c>
@@ -35780,7 +35774,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A69" s="10" t="s">
         <v>89</v>
       </c>
@@ -35812,7 +35806,7 @@
         <v>4291</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A70" s="10" t="s">
         <v>90</v>
       </c>
@@ -35844,7 +35838,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A71" s="10" t="s">
         <v>164</v>
       </c>
@@ -35876,7 +35870,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A72" s="10" t="s">
         <v>92</v>
       </c>
@@ -35908,7 +35902,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A73" s="10" t="s">
         <v>93</v>
       </c>
@@ -35940,7 +35934,7 @@
         <v>2568</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A74" s="10" t="s">
         <v>94</v>
       </c>
@@ -35972,7 +35966,7 @@
         <v>3920</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A75" s="10" t="s">
         <v>95</v>
       </c>
@@ -36004,7 +35998,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A76" s="10" t="s">
         <v>96</v>
       </c>
@@ -36036,7 +36030,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A77" s="10" t="s">
         <v>97</v>
       </c>
@@ -36068,7 +36062,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A78" s="10" t="s">
         <v>98</v>
       </c>
@@ -36100,7 +36094,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A79" s="10" t="s">
         <v>99</v>
       </c>
@@ -36132,7 +36126,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A80" s="10" t="s">
         <v>187</v>
       </c>
@@ -36164,7 +36158,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A81" s="10" t="s">
         <v>194</v>
       </c>
@@ -36196,7 +36190,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A82" s="10" t="s">
         <v>100</v>
       </c>
@@ -36228,7 +36222,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A83" s="10" t="s">
         <v>101</v>
       </c>
@@ -36260,7 +36254,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A84" s="10" t="s">
         <v>102</v>
       </c>
@@ -36292,7 +36286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A85" s="11" t="s">
         <v>166</v>
       </c>
@@ -36324,7 +36318,7 @@
         <v>18982</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A86" s="9"/>
       <c r="B86" s="67" t="s">
         <v>63</v>
@@ -36338,7 +36332,7 @@
       <c r="I86" s="67"/>
       <c r="J86" s="67"/>
     </row>
-    <row r="87" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A87" t="s">
         <v>24</v>
       </c>
@@ -36352,7 +36346,7 @@
       <c r="I87" s="36"/>
       <c r="J87" s="36"/>
     </row>
-    <row r="88" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A88" s="10" t="s">
         <v>163</v>
       </c>
@@ -36384,7 +36378,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A89" s="10" t="s">
         <v>89</v>
       </c>
@@ -36416,7 +36410,7 @@
         <v>52276</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A90" s="10" t="s">
         <v>90</v>
       </c>
@@ -36448,7 +36442,7 @@
         <v>5266</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A91" s="10" t="s">
         <v>164</v>
       </c>
@@ -36480,7 +36474,7 @@
         <v>15198</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A92" s="10" t="s">
         <v>92</v>
       </c>
@@ -36512,7 +36506,7 @@
         <v>2860</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A93" s="10" t="s">
         <v>93</v>
       </c>
@@ -36544,7 +36538,7 @@
         <v>11043</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A94" s="10" t="s">
         <v>94</v>
       </c>
@@ -36576,7 +36570,7 @@
         <v>37829</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A95" s="10" t="s">
         <v>95</v>
       </c>
@@ -36608,7 +36602,7 @@
         <v>8636</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A96" s="10" t="s">
         <v>96</v>
       </c>
@@ -36640,7 +36634,7 @@
         <v>33777</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A97" s="10" t="s">
         <v>97</v>
       </c>
@@ -36672,7 +36666,7 @@
         <v>12869</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A98" s="10" t="s">
         <v>98</v>
       </c>
@@ -36704,7 +36698,7 @@
         <v>13664</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A99" s="10" t="s">
         <v>99</v>
       </c>
@@ -36736,7 +36730,7 @@
         <v>19982</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A100" s="10" t="s">
         <v>187</v>
       </c>
@@ -36768,7 +36762,7 @@
         <v>179343</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A101" s="10" t="s">
         <v>194</v>
       </c>
@@ -36800,7 +36794,7 @@
         <v>45029</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A102" s="10" t="s">
         <v>100</v>
       </c>
@@ -36832,7 +36826,7 @@
         <v>3592</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A103" s="10" t="s">
         <v>101</v>
       </c>
@@ -36864,7 +36858,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A104" s="10" t="s">
         <v>102</v>
       </c>
@@ -36896,7 +36890,7 @@
         <v>3454</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A105" s="11" t="s">
         <v>166</v>
       </c>
@@ -36928,7 +36922,7 @@
         <v>447122</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B106" s="40"/>
       <c r="C106" s="40"/>
       <c r="D106" s="40"/>
@@ -36939,7 +36933,7 @@
       <c r="I106" s="40"/>
       <c r="J106" s="40"/>
     </row>
-    <row r="107" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -36953,7 +36947,7 @@
       <c r="I107" s="36"/>
       <c r="J107" s="36"/>
     </row>
-    <row r="108" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A108" s="10" t="s">
         <v>163</v>
       </c>
@@ -36985,7 +36979,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A109" s="10" t="s">
         <v>89</v>
       </c>
@@ -37017,7 +37011,7 @@
         <v>2353</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A110" s="10" t="s">
         <v>90</v>
       </c>
@@ -37049,7 +37043,7 @@
         <v>2503</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A111" s="10" t="s">
         <v>164</v>
       </c>
@@ -37081,7 +37075,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A112" s="10" t="s">
         <v>92</v>
       </c>
@@ -37113,7 +37107,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A113" s="10" t="s">
         <v>93</v>
       </c>
@@ -37145,7 +37139,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A114" s="10" t="s">
         <v>94</v>
       </c>
@@ -37177,7 +37171,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A115" s="10" t="s">
         <v>95</v>
       </c>
@@ -37209,7 +37203,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A116" s="10" t="s">
         <v>96</v>
       </c>
@@ -37241,7 +37235,7 @@
         <v>2763</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A117" s="10" t="s">
         <v>97</v>
       </c>
@@ -37273,7 +37267,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A118" s="10" t="s">
         <v>98</v>
       </c>
@@ -37305,7 +37299,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A119" s="10" t="s">
         <v>99</v>
       </c>
@@ -37337,7 +37331,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A120" s="10" t="s">
         <v>187</v>
       </c>
@@ -37369,7 +37363,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A121" s="10" t="s">
         <v>194</v>
       </c>
@@ -37401,7 +37395,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A122" s="10" t="s">
         <v>100</v>
       </c>
@@ -37433,7 +37427,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A123" s="10" t="s">
         <v>101</v>
       </c>
@@ -37465,7 +37459,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A124" s="10" t="s">
         <v>102</v>
       </c>
@@ -37497,7 +37491,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A125" s="11" t="s">
         <v>166</v>
       </c>
@@ -37529,7 +37523,7 @@
         <v>12763</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B126" s="40"/>
       <c r="C126" s="40"/>
       <c r="D126" s="40"/>
@@ -37540,7 +37534,7 @@
       <c r="I126" s="40"/>
       <c r="J126" s="40"/>
     </row>
-    <row r="127" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A127" t="s">
         <v>41</v>
       </c>
@@ -37554,7 +37548,7 @@
       <c r="I127" s="36"/>
       <c r="J127" s="36"/>
     </row>
-    <row r="128" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A128" s="10" t="s">
         <v>163</v>
       </c>
@@ -37586,7 +37580,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A129" s="10" t="s">
         <v>89</v>
       </c>
@@ -37618,7 +37612,7 @@
         <v>45574</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A130" s="10" t="s">
         <v>90</v>
       </c>
@@ -37650,7 +37644,7 @@
         <v>2522</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A131" s="10" t="s">
         <v>164</v>
       </c>
@@ -37682,7 +37676,7 @@
         <v>13676</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A132" s="10" t="s">
         <v>92</v>
       </c>
@@ -37714,7 +37708,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A133" s="10" t="s">
         <v>93</v>
       </c>
@@ -37746,7 +37740,7 @@
         <v>6811</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A134" s="10" t="s">
         <v>94</v>
       </c>
@@ -37778,7 +37772,7 @@
         <v>33398</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A135" s="10" t="s">
         <v>95</v>
       </c>
@@ -37810,7 +37804,7 @@
         <v>8030</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A136" s="10" t="s">
         <v>96</v>
       </c>
@@ -37842,7 +37836,7 @@
         <v>30445</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A137" s="10" t="s">
         <v>97</v>
       </c>
@@ -37874,7 +37868,7 @@
         <v>11895</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A138" s="10" t="s">
         <v>98</v>
       </c>
@@ -37906,7 +37900,7 @@
         <v>12255</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A139" s="10" t="s">
         <v>99</v>
       </c>
@@ -37938,7 +37932,7 @@
         <v>18991</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A140" s="10" t="s">
         <v>187</v>
       </c>
@@ -37970,7 +37964,7 @@
         <v>177583</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A141" s="10" t="s">
         <v>194</v>
       </c>
@@ -38002,7 +37996,7 @@
         <v>44207</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A142" s="10" t="s">
         <v>100</v>
       </c>
@@ -38034,7 +38028,7 @@
         <v>3542</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A143" s="10" t="s">
         <v>101</v>
       </c>
@@ -38066,7 +38060,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A144" s="10" t="s">
         <v>102</v>
       </c>
@@ -38098,7 +38092,7 @@
         <v>3430</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A145" s="11" t="s">
         <v>166</v>
       </c>
@@ -38130,7 +38124,7 @@
         <v>414586</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B146" s="40"/>
       <c r="C146" s="40"/>
       <c r="D146" s="40"/>
@@ -38141,7 +38135,7 @@
       <c r="I146" s="40"/>
       <c r="J146" s="40"/>
     </row>
-    <row r="147" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A147" t="s">
         <v>42</v>
       </c>
@@ -38155,7 +38149,7 @@
       <c r="I147" s="36"/>
       <c r="J147" s="36"/>
     </row>
-    <row r="148" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A148" s="10" t="s">
         <v>163</v>
       </c>
@@ -38187,7 +38181,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A149" s="10" t="s">
         <v>89</v>
       </c>
@@ -38219,7 +38213,7 @@
         <v>4344</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A150" s="10" t="s">
         <v>90</v>
       </c>
@@ -38251,7 +38245,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A151" s="10" t="s">
         <v>164</v>
       </c>
@@ -38283,7 +38277,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A152" s="10" t="s">
         <v>92</v>
       </c>
@@ -38315,7 +38309,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A153" s="10" t="s">
         <v>93</v>
       </c>
@@ -38347,7 +38341,7 @@
         <v>3106</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A154" s="10" t="s">
         <v>94</v>
       </c>
@@ -38379,7 +38373,7 @@
         <v>4126</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A155" s="10" t="s">
         <v>95</v>
       </c>
@@ -38411,7 +38405,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A156" s="10" t="s">
         <v>96</v>
       </c>
@@ -38443,7 +38437,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A157" s="10" t="s">
         <v>97</v>
       </c>
@@ -38475,7 +38469,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A158" s="10" t="s">
         <v>98</v>
       </c>
@@ -38507,7 +38501,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A159" s="10" t="s">
         <v>99</v>
       </c>
@@ -38539,7 +38533,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A160" s="10" t="s">
         <v>187</v>
       </c>
@@ -38571,7 +38565,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A161" s="10" t="s">
         <v>194</v>
       </c>
@@ -38603,7 +38597,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A162" s="10" t="s">
         <v>100</v>
       </c>
@@ -38635,7 +38629,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A163" s="10" t="s">
         <v>101</v>
       </c>
@@ -38667,7 +38661,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A164" s="10" t="s">
         <v>102</v>
       </c>
@@ -38699,7 +38693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A165" s="11" t="s">
         <v>166</v>
       </c>
@@ -38731,7 +38725,7 @@
         <v>19775</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="166" ht="30" customHeight="1" thickBot="1" ns3:dyDescent="0.35">
       <c r="A166" s="64" t="s">
         <v>133</v>
       </c>
@@ -38745,7 +38739,7 @@
       <c r="I166" s="64"/>
       <c r="J166" s="64"/>
     </row>
-    <row r="167" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="167" ht="15.75" customHeight="1" thickTop="1" ns3:dyDescent="0.25">
       <c r="A167" s="70" t="s">
         <v>173</v>
       </c>
@@ -38759,7 +38753,7 @@
       <c r="I167" s="70"/>
       <c r="J167" s="70"/>
     </row>
-    <row r="168" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A168" s="58" t="s">
         <v>135</v>
       </c>
@@ -38773,7 +38767,7 @@
       <c r="I168" s="58"/>
       <c r="J168" s="58"/>
     </row>
-    <row r="169" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A169" s="63" t="s">
         <v>75</v>
       </c>
@@ -38787,7 +38781,7 @@
       <c r="I169" s="63"/>
       <c r="J169" s="63"/>
     </row>
-    <row r="170" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A170" s="63" t="s">
         <v>185</v>
       </c>
@@ -38801,7 +38795,7 @@
       <c r="I170" s="63"/>
       <c r="J170" s="63"/>
     </row>
-    <row r="171" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A171" s="63" t="s">
         <v>186</v>
       </c>
@@ -38815,7 +38809,7 @@
       <c r="I171" s="63"/>
       <c r="J171" s="63"/>
     </row>
-    <row r="172" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" ht="31.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A172" s="59" t="s">
         <v>168</v>
       </c>
@@ -38829,7 +38823,7 @@
       <c r="I172" s="59"/>
       <c r="J172" s="59"/>
     </row>
-    <row r="173" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A173" s="63" t="s">
         <v>167</v>
       </c>
@@ -38843,7 +38837,7 @@
       <c r="I173" s="63"/>
       <c r="J173" s="63"/>
     </row>
-    <row r="174" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" ht="31.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A174" s="69" t="s">
         <v>265</v>
       </c>
@@ -38857,7 +38851,7 @@
       <c r="I174" s="69"/>
       <c r="J174" s="69"/>
     </row>
-    <row r="175" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A175" s="62" t="s">
         <v>5</v>
       </c>
@@ -38891,7 +38885,7 @@
     <mergeCell ref="A172:J172"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A175" r:id="rId1" location="copyright-and-creative-commons" xr:uid="{3076E81C-DFA4-4726-9645-B4EA6A599651}"/>
+    <hyperlink ref="A175" r:id="rId1" location="copyright-and-creative-commons" ns2:uid="{3076E81C-DFA4-4726-9645-B4EA6A599651}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -38900,21 +38894,20 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25C6D08E-9286-4C2E-8DC3-72535BF6C92A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{25C6D08E-9286-4C2E-8DC3-72535BF6C92A}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:I174"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.125" customWidth="1"/>
     <col min="2" max="2" width="11.25" customWidth="1"/>
     <col min="3" max="5" width="13.25" customWidth="1"/>
     <col min="6" max="9" width="11.25" customWidth="1"/>
-    <col min="10" max="16384" width="8.625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="65.25" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="66" t="s">
         <v>193</v>
       </c>
@@ -38927,7 +38920,7 @@
       <c r="H1" s="66"/>
       <c r="I1" s="66"/>
     </row>
-    <row r="2" spans="1:9" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="36" customHeight="1" thickBot="1" ns3:dyDescent="0.35">
       <c r="A2" s="71" t="s">
         <v>109</v>
       </c>
@@ -38940,7 +38933,7 @@
       <c r="H2" s="71"/>
       <c r="I2" s="71"/>
     </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15.75" customHeight="1" thickTop="1" ns3:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>83</v>
       </c>
@@ -38953,8 +38946,8 @@
       <c r="H3" s="58"/>
       <c r="I3" s="58"/>
     </row>
-    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:9" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.75" customHeight="1" ns3:dyDescent="0.25"/>
+    <row r="5" ht="64.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>162</v>
       </c>
@@ -38983,7 +38976,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="67" t="s">
         <v>87</v>
@@ -38996,7 +38989,7 @@
       <c r="H6" s="67"/>
       <c r="I6" s="67"/>
     </row>
-    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -39009,7 +39002,7 @@
       <c r="H7" s="36"/>
       <c r="I7" s="36"/>
     </row>
-    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>163</v>
       </c>
@@ -39038,7 +39031,7 @@
         <v>62.4</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>89</v>
       </c>
@@ -39067,7 +39060,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>90</v>
       </c>
@@ -39096,7 +39089,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>164</v>
       </c>
@@ -39125,7 +39118,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>92</v>
       </c>
@@ -39154,7 +39147,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>93</v>
       </c>
@@ -39183,7 +39176,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>94</v>
       </c>
@@ -39212,7 +39205,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>95</v>
       </c>
@@ -39241,7 +39234,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>96</v>
       </c>
@@ -39270,7 +39263,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>97</v>
       </c>
@@ -39299,7 +39292,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>98</v>
       </c>
@@ -39328,7 +39321,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>99</v>
       </c>
@@ -39357,7 +39350,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>187</v>
       </c>
@@ -39386,7 +39379,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>165</v>
       </c>
@@ -39415,7 +39408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>100</v>
       </c>
@@ -39444,7 +39437,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>101</v>
       </c>
@@ -39473,7 +39466,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>102</v>
       </c>
@@ -39502,7 +39495,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>166</v>
       </c>
@@ -39531,7 +39524,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B26" s="40"/>
       <c r="C26" s="40"/>
       <c r="D26" s="40"/>
@@ -39541,7 +39534,7 @@
       <c r="H26" s="40"/>
       <c r="I26" s="40"/>
     </row>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -39554,7 +39547,7 @@
       <c r="H27" s="36"/>
       <c r="I27" s="36"/>
     </row>
-    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>163</v>
       </c>
@@ -39583,7 +39576,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>89</v>
       </c>
@@ -39612,7 +39605,7 @@
         <v>38.6</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>90</v>
       </c>
@@ -39641,7 +39634,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>164</v>
       </c>
@@ -39670,7 +39663,7 @@
         <v>37.700000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>92</v>
       </c>
@@ -39699,7 +39692,7 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>93</v>
       </c>
@@ -39728,7 +39721,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>94</v>
       </c>
@@ -39757,7 +39750,7 @@
         <v>42.4</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>95</v>
       </c>
@@ -39786,7 +39779,7 @@
         <v>48.7</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>96</v>
       </c>
@@ -39815,7 +39808,7 @@
         <v>37.1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>97</v>
       </c>
@@ -39844,7 +39837,7 @@
         <v>30.4</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>98</v>
       </c>
@@ -39873,7 +39866,7 @@
         <v>33.1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>99</v>
       </c>
@@ -39902,7 +39895,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>187</v>
       </c>
@@ -39931,7 +39924,7 @@
         <v>36.9</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A41" s="10" t="s">
         <v>165</v>
       </c>
@@ -39960,7 +39953,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>100</v>
       </c>
@@ -39989,7 +39982,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>101</v>
       </c>
@@ -40018,7 +40011,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>102</v>
       </c>
@@ -40047,7 +40040,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>166</v>
       </c>
@@ -40076,7 +40069,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B46" s="40"/>
       <c r="C46" s="40"/>
       <c r="D46" s="40"/>
@@ -40086,7 +40079,7 @@
       <c r="H46" s="40"/>
       <c r="I46" s="40"/>
     </row>
-    <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A47" t="s">
         <v>41</v>
       </c>
@@ -40099,7 +40092,7 @@
       <c r="H47" s="36"/>
       <c r="I47" s="36"/>
     </row>
-    <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>163</v>
       </c>
@@ -40128,7 +40121,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>89</v>
       </c>
@@ -40157,7 +40150,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>90</v>
       </c>
@@ -40186,7 +40179,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>164</v>
       </c>
@@ -40215,7 +40208,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A52" s="10" t="s">
         <v>92</v>
       </c>
@@ -40244,7 +40237,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>93</v>
       </c>
@@ -40273,7 +40266,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A54" s="10" t="s">
         <v>94</v>
       </c>
@@ -40302,7 +40295,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>95</v>
       </c>
@@ -40331,7 +40324,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A56" s="10" t="s">
         <v>96</v>
       </c>
@@ -40360,7 +40353,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>97</v>
       </c>
@@ -40389,7 +40382,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A58" s="10" t="s">
         <v>98</v>
       </c>
@@ -40418,7 +40411,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>99</v>
       </c>
@@ -40447,7 +40440,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>187</v>
       </c>
@@ -40476,7 +40469,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A61" s="10" t="s">
         <v>165</v>
       </c>
@@ -40505,7 +40498,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A62" s="10" t="s">
         <v>100</v>
       </c>
@@ -40534,7 +40527,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A63" s="10" t="s">
         <v>101</v>
       </c>
@@ -40563,7 +40556,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A64" s="10" t="s">
         <v>102</v>
       </c>
@@ -40592,7 +40585,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A65" s="11" t="s">
         <v>166</v>
       </c>
@@ -40621,7 +40614,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B66" s="40"/>
       <c r="C66" s="40"/>
       <c r="D66" s="40"/>
@@ -40631,7 +40624,7 @@
       <c r="H66" s="40"/>
       <c r="I66" s="40"/>
     </row>
-    <row r="67" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A67" t="s">
         <v>42</v>
       </c>
@@ -40644,7 +40637,7 @@
       <c r="H67" s="36"/>
       <c r="I67" s="36"/>
     </row>
-    <row r="68" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A68" s="10" t="s">
         <v>163</v>
       </c>
@@ -40673,7 +40666,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A69" s="10" t="s">
         <v>89</v>
       </c>
@@ -40702,7 +40695,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A70" s="10" t="s">
         <v>90</v>
       </c>
@@ -40731,7 +40724,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A71" s="10" t="s">
         <v>164</v>
       </c>
@@ -40760,7 +40753,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A72" s="10" t="s">
         <v>92</v>
       </c>
@@ -40789,7 +40782,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A73" s="10" t="s">
         <v>93</v>
       </c>
@@ -40818,7 +40811,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A74" s="10" t="s">
         <v>94</v>
       </c>
@@ -40847,7 +40840,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A75" s="10" t="s">
         <v>95</v>
       </c>
@@ -40876,7 +40869,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A76" s="10" t="s">
         <v>96</v>
       </c>
@@ -40905,7 +40898,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A77" s="10" t="s">
         <v>97</v>
       </c>
@@ -40934,7 +40927,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A78" s="10" t="s">
         <v>98</v>
       </c>
@@ -40963,7 +40956,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A79" s="10" t="s">
         <v>99</v>
       </c>
@@ -40992,7 +40985,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A80" s="10" t="s">
         <v>187</v>
       </c>
@@ -41021,7 +41014,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A81" s="10" t="s">
         <v>165</v>
       </c>
@@ -41050,7 +41043,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A82" s="10" t="s">
         <v>100</v>
       </c>
@@ -41079,7 +41072,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A83" s="10" t="s">
         <v>101</v>
       </c>
@@ -41108,7 +41101,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A84" s="10" t="s">
         <v>102</v>
       </c>
@@ -41137,7 +41130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A85" s="11" t="s">
         <v>166</v>
       </c>
@@ -41166,7 +41159,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A86" s="9"/>
       <c r="B86" s="67" t="s">
         <v>63</v>
@@ -41179,7 +41172,7 @@
       <c r="H86" s="67"/>
       <c r="I86" s="67"/>
     </row>
-    <row r="87" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A87" t="s">
         <v>24</v>
       </c>
@@ -41192,7 +41185,7 @@
       <c r="H87" s="36"/>
       <c r="I87" s="36"/>
     </row>
-    <row r="88" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A88" s="10" t="s">
         <v>163</v>
       </c>
@@ -41221,7 +41214,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A89" s="10" t="s">
         <v>89</v>
       </c>
@@ -41250,7 +41243,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A90" s="10" t="s">
         <v>90</v>
       </c>
@@ -41279,7 +41272,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A91" s="10" t="s">
         <v>164</v>
       </c>
@@ -41308,7 +41301,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A92" s="10" t="s">
         <v>92</v>
       </c>
@@ -41337,7 +41330,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A93" s="10" t="s">
         <v>93</v>
       </c>
@@ -41366,7 +41359,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A94" s="10" t="s">
         <v>94</v>
       </c>
@@ -41395,7 +41388,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A95" s="10" t="s">
         <v>95</v>
       </c>
@@ -41424,7 +41417,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A96" s="10" t="s">
         <v>96</v>
       </c>
@@ -41453,7 +41446,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A97" s="10" t="s">
         <v>97</v>
       </c>
@@ -41482,7 +41475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A98" s="10" t="s">
         <v>98</v>
       </c>
@@ -41511,7 +41504,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A99" s="10" t="s">
         <v>99</v>
       </c>
@@ -41540,7 +41533,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A100" s="10" t="s">
         <v>187</v>
       </c>
@@ -41569,7 +41562,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A101" s="10" t="s">
         <v>165</v>
       </c>
@@ -41598,7 +41591,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A102" s="10" t="s">
         <v>100</v>
       </c>
@@ -41627,7 +41620,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A103" s="10" t="s">
         <v>101</v>
       </c>
@@ -41656,7 +41649,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A104" s="10" t="s">
         <v>102</v>
       </c>
@@ -41685,7 +41678,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A105" s="11" t="s">
         <v>166</v>
       </c>
@@ -41714,7 +41707,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B106" s="40"/>
       <c r="C106" s="40"/>
       <c r="D106" s="40"/>
@@ -41724,7 +41717,7 @@
       <c r="H106" s="40"/>
       <c r="I106" s="40"/>
     </row>
-    <row r="107" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -41737,7 +41730,7 @@
       <c r="H107" s="36"/>
       <c r="I107" s="36"/>
     </row>
-    <row r="108" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A108" s="10" t="s">
         <v>163</v>
       </c>
@@ -41766,7 +41759,7 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A109" s="10" t="s">
         <v>89</v>
       </c>
@@ -41795,7 +41788,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A110" s="10" t="s">
         <v>90</v>
       </c>
@@ -41824,7 +41817,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A111" s="10" t="s">
         <v>164</v>
       </c>
@@ -41853,7 +41846,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A112" s="10" t="s">
         <v>92</v>
       </c>
@@ -41882,7 +41875,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A113" s="10" t="s">
         <v>93</v>
       </c>
@@ -41911,7 +41904,7 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A114" s="10" t="s">
         <v>94</v>
       </c>
@@ -41940,7 +41933,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A115" s="10" t="s">
         <v>95</v>
       </c>
@@ -41969,7 +41962,7 @@
         <v>56.4</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A116" s="10" t="s">
         <v>96</v>
       </c>
@@ -41998,7 +41991,7 @@
         <v>36.299999999999997</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A117" s="10" t="s">
         <v>97</v>
       </c>
@@ -42027,7 +42020,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A118" s="10" t="s">
         <v>98</v>
       </c>
@@ -42056,7 +42049,7 @@
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A119" s="10" t="s">
         <v>99</v>
       </c>
@@ -42085,7 +42078,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A120" s="10" t="s">
         <v>187</v>
       </c>
@@ -42114,7 +42107,7 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A121" s="10" t="s">
         <v>165</v>
       </c>
@@ -42143,7 +42136,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A122" s="10" t="s">
         <v>100</v>
       </c>
@@ -42172,7 +42165,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A123" s="10" t="s">
         <v>101</v>
       </c>
@@ -42201,7 +42194,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A124" s="10" t="s">
         <v>102</v>
       </c>
@@ -42230,7 +42223,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A125" s="11" t="s">
         <v>166</v>
       </c>
@@ -42259,7 +42252,7 @@
         <v>37.9</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B126" s="40"/>
       <c r="C126" s="40"/>
       <c r="D126" s="40"/>
@@ -42269,7 +42262,7 @@
       <c r="H126" s="40"/>
       <c r="I126" s="40"/>
     </row>
-    <row r="127" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A127" t="s">
         <v>41</v>
       </c>
@@ -42282,7 +42275,7 @@
       <c r="H127" s="36"/>
       <c r="I127" s="36"/>
     </row>
-    <row r="128" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A128" s="10" t="s">
         <v>163</v>
       </c>
@@ -42311,7 +42304,7 @@
         <v>30.4</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A129" s="10" t="s">
         <v>89</v>
       </c>
@@ -42340,7 +42333,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A130" s="10" t="s">
         <v>90</v>
       </c>
@@ -42369,7 +42362,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A131" s="10" t="s">
         <v>164</v>
       </c>
@@ -42398,7 +42391,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A132" s="10" t="s">
         <v>92</v>
       </c>
@@ -42427,7 +42420,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A133" s="10" t="s">
         <v>93</v>
       </c>
@@ -42456,7 +42449,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A134" s="10" t="s">
         <v>94</v>
       </c>
@@ -42485,7 +42478,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A135" s="10" t="s">
         <v>95</v>
       </c>
@@ -42514,7 +42507,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A136" s="10" t="s">
         <v>96</v>
       </c>
@@ -42543,7 +42536,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A137" s="10" t="s">
         <v>97</v>
       </c>
@@ -42572,7 +42565,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A138" s="10" t="s">
         <v>98</v>
       </c>
@@ -42601,7 +42594,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A139" s="10" t="s">
         <v>99</v>
       </c>
@@ -42630,7 +42623,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A140" s="10" t="s">
         <v>187</v>
       </c>
@@ -42659,7 +42652,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A141" s="10" t="s">
         <v>165</v>
       </c>
@@ -42688,7 +42681,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A142" s="10" t="s">
         <v>100</v>
       </c>
@@ -42717,7 +42710,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A143" s="10" t="s">
         <v>101</v>
       </c>
@@ -42746,7 +42739,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A144" s="10" t="s">
         <v>102</v>
       </c>
@@ -42775,7 +42768,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A145" s="11" t="s">
         <v>166</v>
       </c>
@@ -42804,7 +42797,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="B146" s="40"/>
       <c r="C146" s="40"/>
       <c r="D146" s="40"/>
@@ -42814,7 +42807,7 @@
       <c r="H146" s="40"/>
       <c r="I146" s="40"/>
     </row>
-    <row r="147" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A147" t="s">
         <v>42</v>
       </c>
@@ -42827,7 +42820,7 @@
       <c r="H147" s="36"/>
       <c r="I147" s="36"/>
     </row>
-    <row r="148" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A148" s="10" t="s">
         <v>163</v>
       </c>
@@ -42856,7 +42849,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A149" s="10" t="s">
         <v>89</v>
       </c>
@@ -42885,7 +42878,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A150" s="10" t="s">
         <v>90</v>
       </c>
@@ -42914,7 +42907,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A151" s="10" t="s">
         <v>164</v>
       </c>
@@ -42943,7 +42936,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A152" s="10" t="s">
         <v>92</v>
       </c>
@@ -42972,7 +42965,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A153" s="10" t="s">
         <v>93</v>
       </c>
@@ -43001,7 +42994,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A154" s="10" t="s">
         <v>94</v>
       </c>
@@ -43030,7 +43023,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A155" s="10" t="s">
         <v>95</v>
       </c>
@@ -43059,7 +43052,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A156" s="10" t="s">
         <v>96</v>
       </c>
@@ -43088,7 +43081,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A157" s="10" t="s">
         <v>97</v>
       </c>
@@ -43117,7 +43110,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A158" s="10" t="s">
         <v>98</v>
       </c>
@@ -43146,7 +43139,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A159" s="10" t="s">
         <v>99</v>
       </c>
@@ -43175,7 +43168,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A160" s="10" t="s">
         <v>187</v>
       </c>
@@ -43204,7 +43197,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A161" s="10" t="s">
         <v>165</v>
       </c>
@@ -43233,7 +43226,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A162" s="10" t="s">
         <v>100</v>
       </c>
@@ -43262,7 +43255,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A163" s="10" t="s">
         <v>101</v>
       </c>
@@ -43291,7 +43284,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A164" s="10" t="s">
         <v>102</v>
       </c>
@@ -43320,7 +43313,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" ht="25.7" customHeight="1" ns3:dyDescent="0.25">
       <c r="A165" s="11" t="s">
         <v>166</v>
       </c>
@@ -43349,7 +43342,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="166" ht="30" customHeight="1" thickBot="1" ns3:dyDescent="0.35">
       <c r="A166" s="64" t="s">
         <v>133</v>
       </c>
@@ -43362,7 +43355,7 @@
       <c r="H166" s="64"/>
       <c r="I166" s="64"/>
     </row>
-    <row r="167" spans="1:9" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="167" ht="15.75" customHeight="1" thickTop="1" ns3:dyDescent="0.25">
       <c r="A167" s="70" t="s">
         <v>173</v>
       </c>
@@ -43375,7 +43368,7 @@
       <c r="H167" s="70"/>
       <c r="I167" s="70"/>
     </row>
-    <row r="168" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A168" s="63" t="s">
         <v>135</v>
       </c>
@@ -43388,7 +43381,7 @@
       <c r="H168" s="63"/>
       <c r="I168" s="63"/>
     </row>
-    <row r="169" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A169" s="61" t="s">
         <v>192</v>
       </c>
@@ -43401,7 +43394,7 @@
       <c r="H169" s="61"/>
       <c r="I169" s="61"/>
     </row>
-    <row r="170" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A170" s="63" t="s">
         <v>185</v>
       </c>
@@ -43414,7 +43407,7 @@
       <c r="H170" s="63"/>
       <c r="I170" s="63"/>
     </row>
-    <row r="171" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A171" s="63" t="s">
         <v>186</v>
       </c>
@@ -43427,7 +43420,7 @@
       <c r="H171" s="63"/>
       <c r="I171" s="63"/>
     </row>
-    <row r="172" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" ht="31.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A172" s="59" t="s">
         <v>168</v>
       </c>
@@ -43440,7 +43433,7 @@
       <c r="H172" s="59"/>
       <c r="I172" s="59"/>
     </row>
-    <row r="173" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A173" s="63" t="s">
         <v>167</v>
       </c>
@@ -43453,7 +43446,7 @@
       <c r="H173" s="63"/>
       <c r="I173" s="63"/>
     </row>
-    <row r="174" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A174" s="62" t="s">
         <v>5</v>
       </c>
@@ -43485,7 +43478,7 @@
     <mergeCell ref="A171:I171"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A174" r:id="rId1" location="copyright-and-creative-commons" xr:uid="{1421A964-B26A-4EE3-902B-A6B2D440E8AA}"/>
+    <hyperlink ref="A174" r:id="rId1" location="copyright-and-creative-commons" ns2:uid="{1421A964-B26A-4EE3-902B-A6B2D440E8AA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
